--- a/thaco/color/Office-1 v2.xlsx
+++ b/thaco/color/Office-1 v2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/design/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A18D02-9565-5E49-A2A3-A6B114504B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{887BEDE2-B35C-154E-A24A-5C10FB1E2765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="320" yWindow="500" windowWidth="38080" windowHeight="20780" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6484,7 +6484,83 @@
     <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="18" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6503,131 +6579,67 @@
     <xf numFmtId="164" fontId="16" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="18" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="16" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="18" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6645,66 +6657,162 @@
     <xf numFmtId="165" fontId="5" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="43" fontId="18" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="21" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6713,184 +6821,76 @@
     <xf numFmtId="0" fontId="16" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="16" fillId="2" borderId="22" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="16" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="16" fillId="2" borderId="19" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="16" fillId="2" borderId="16" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="12" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="16" fillId="2" borderId="22" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="16" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="16" fillId="2" borderId="19" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="16" fillId="2" borderId="16" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7811,84 +7811,84 @@
       <c r="CB1" s="14"/>
     </row>
     <row r="2" spans="1:85" s="3" customFormat="1" outlineLevel="1">
-      <c r="A2" s="322" t="s">
+      <c r="A2" s="288" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="284" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="323" t="s">
+      <c r="C2" s="289" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="323" t="s">
+      <c r="D2" s="289" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="284" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="320" t="s">
+      <c r="F2" s="287" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="320" t="s">
+      <c r="G2" s="287" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="320" t="s">
+      <c r="H2" s="287" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="320" t="s">
+      <c r="I2" s="287" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="321" t="s">
+      <c r="J2" s="290" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="297"/>
-      <c r="L2" s="297"/>
-      <c r="M2" s="297"/>
-      <c r="N2" s="297"/>
-      <c r="O2" s="297"/>
-      <c r="P2" s="297"/>
-      <c r="Q2" s="297"/>
-      <c r="R2" s="297"/>
-      <c r="S2" s="297"/>
-      <c r="T2" s="297"/>
-      <c r="U2" s="297"/>
-      <c r="V2" s="297"/>
-      <c r="W2" s="297"/>
-      <c r="X2" s="320" t="s">
+      <c r="K2" s="291"/>
+      <c r="L2" s="291"/>
+      <c r="M2" s="291"/>
+      <c r="N2" s="291"/>
+      <c r="O2" s="291"/>
+      <c r="P2" s="291"/>
+      <c r="Q2" s="291"/>
+      <c r="R2" s="291"/>
+      <c r="S2" s="291"/>
+      <c r="T2" s="291"/>
+      <c r="U2" s="291"/>
+      <c r="V2" s="291"/>
+      <c r="W2" s="291"/>
+      <c r="X2" s="287" t="s">
         <v>11</v>
       </c>
-      <c r="Y2" s="297"/>
-      <c r="Z2" s="297"/>
-      <c r="AA2" s="297"/>
-      <c r="AB2" s="297"/>
-      <c r="AC2" s="297"/>
-      <c r="AD2" s="297"/>
-      <c r="AE2" s="297"/>
-      <c r="AF2" s="297"/>
-      <c r="AG2" s="297"/>
-      <c r="AH2" s="297"/>
-      <c r="AI2" s="297"/>
-      <c r="AJ2" s="297"/>
-      <c r="AK2" s="297"/>
-      <c r="AL2" s="297"/>
-      <c r="AM2" s="297"/>
-      <c r="AN2" s="298"/>
-      <c r="AO2" s="320" t="s">
+      <c r="Y2" s="291"/>
+      <c r="Z2" s="291"/>
+      <c r="AA2" s="291"/>
+      <c r="AB2" s="291"/>
+      <c r="AC2" s="291"/>
+      <c r="AD2" s="291"/>
+      <c r="AE2" s="291"/>
+      <c r="AF2" s="291"/>
+      <c r="AG2" s="291"/>
+      <c r="AH2" s="291"/>
+      <c r="AI2" s="291"/>
+      <c r="AJ2" s="291"/>
+      <c r="AK2" s="291"/>
+      <c r="AL2" s="291"/>
+      <c r="AM2" s="291"/>
+      <c r="AN2" s="292"/>
+      <c r="AO2" s="287" t="s">
         <v>12</v>
       </c>
-      <c r="AP2" s="320" t="s">
+      <c r="AP2" s="287" t="s">
         <v>13</v>
       </c>
-      <c r="AQ2" s="320" t="s">
+      <c r="AQ2" s="287" t="s">
         <v>14</v>
       </c>
-      <c r="AR2" s="320" t="s">
+      <c r="AR2" s="287" t="s">
         <v>15</v>
       </c>
-      <c r="AS2" s="320" t="s">
+      <c r="AS2" s="287" t="s">
         <v>16</v>
       </c>
-      <c r="AT2" s="320" t="s">
+      <c r="AT2" s="287" t="s">
         <v>17</v>
       </c>
       <c r="AU2" s="284" t="s">
@@ -7903,146 +7903,146 @@
       <c r="AX2" s="284" t="s">
         <v>21</v>
       </c>
-      <c r="AY2" s="297"/>
-      <c r="AZ2" s="297"/>
-      <c r="BA2" s="297"/>
-      <c r="BB2" s="297"/>
-      <c r="BC2" s="297"/>
-      <c r="BD2" s="297"/>
-      <c r="BE2" s="297"/>
-      <c r="BF2" s="297"/>
-      <c r="BG2" s="297"/>
-      <c r="BH2" s="297"/>
-      <c r="BI2" s="297"/>
-      <c r="BJ2" s="297"/>
-      <c r="BK2" s="297"/>
-      <c r="BL2" s="297"/>
-      <c r="BM2" s="297"/>
-      <c r="BN2" s="297"/>
-      <c r="BO2" s="297"/>
-      <c r="BP2" s="298"/>
-      <c r="BQ2" s="292" t="s">
+      <c r="AY2" s="291"/>
+      <c r="AZ2" s="291"/>
+      <c r="BA2" s="291"/>
+      <c r="BB2" s="291"/>
+      <c r="BC2" s="291"/>
+      <c r="BD2" s="291"/>
+      <c r="BE2" s="291"/>
+      <c r="BF2" s="291"/>
+      <c r="BG2" s="291"/>
+      <c r="BH2" s="291"/>
+      <c r="BI2" s="291"/>
+      <c r="BJ2" s="291"/>
+      <c r="BK2" s="291"/>
+      <c r="BL2" s="291"/>
+      <c r="BM2" s="291"/>
+      <c r="BN2" s="291"/>
+      <c r="BO2" s="291"/>
+      <c r="BP2" s="292"/>
+      <c r="BQ2" s="294" t="s">
         <v>22</v>
       </c>
-      <c r="BR2" s="306"/>
-      <c r="BS2" s="292" t="s">
+      <c r="BR2" s="295"/>
+      <c r="BS2" s="294" t="s">
         <v>154</v>
       </c>
-      <c r="BT2" s="289" t="s">
+      <c r="BT2" s="319" t="s">
         <v>155</v>
       </c>
-      <c r="BU2" s="286" t="s">
+      <c r="BU2" s="316" t="s">
         <v>25</v>
       </c>
-      <c r="BV2" s="308" t="s">
+      <c r="BV2" s="298" t="s">
         <v>26</v>
       </c>
-      <c r="BW2" s="309"/>
-      <c r="BX2" s="309"/>
-      <c r="BY2" s="310"/>
-      <c r="BZ2" s="317" t="s">
+      <c r="BW2" s="299"/>
+      <c r="BX2" s="299"/>
+      <c r="BY2" s="300"/>
+      <c r="BZ2" s="307" t="s">
         <v>27</v>
       </c>
-      <c r="CA2" s="317" t="s">
+      <c r="CA2" s="307" t="s">
         <v>28</v>
       </c>
-      <c r="CB2" s="317" t="s">
+      <c r="CB2" s="307" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:85" s="3" customFormat="1" outlineLevel="1">
-      <c r="A3" s="296"/>
-      <c r="B3" s="296"/>
-      <c r="C3" s="296"/>
-      <c r="D3" s="296"/>
-      <c r="E3" s="296"/>
-      <c r="F3" s="296"/>
-      <c r="G3" s="296"/>
-      <c r="H3" s="296"/>
-      <c r="I3" s="296"/>
-      <c r="J3" s="304" t="s">
+      <c r="A3" s="285"/>
+      <c r="B3" s="285"/>
+      <c r="C3" s="285"/>
+      <c r="D3" s="285"/>
+      <c r="E3" s="285"/>
+      <c r="F3" s="285"/>
+      <c r="G3" s="285"/>
+      <c r="H3" s="285"/>
+      <c r="I3" s="285"/>
+      <c r="J3" s="293" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="304" t="s">
+      <c r="K3" s="293" t="s">
         <v>31</v>
       </c>
-      <c r="L3" s="304" t="s">
+      <c r="L3" s="293" t="s">
         <v>32</v>
       </c>
-      <c r="M3" s="304" t="s">
+      <c r="M3" s="293" t="s">
         <v>33</v>
       </c>
-      <c r="N3" s="304" t="s">
+      <c r="N3" s="293" t="s">
         <v>34</v>
       </c>
-      <c r="O3" s="304" t="s">
+      <c r="O3" s="293" t="s">
         <v>35</v>
       </c>
-      <c r="P3" s="304" t="s">
+      <c r="P3" s="293" t="s">
         <v>36</v>
       </c>
-      <c r="Q3" s="304" t="s">
+      <c r="Q3" s="293" t="s">
         <v>37</v>
       </c>
-      <c r="R3" s="304" t="s">
+      <c r="R3" s="293" t="s">
         <v>38</v>
       </c>
-      <c r="S3" s="304" t="s">
+      <c r="S3" s="293" t="s">
         <v>39</v>
       </c>
-      <c r="T3" s="304" t="s">
+      <c r="T3" s="293" t="s">
         <v>40</v>
       </c>
-      <c r="U3" s="305" t="s">
+      <c r="U3" s="310" t="s">
         <v>41</v>
       </c>
-      <c r="V3" s="306"/>
-      <c r="W3" s="304" t="s">
+      <c r="V3" s="295"/>
+      <c r="W3" s="293" t="s">
         <v>42</v>
       </c>
-      <c r="X3" s="300" t="s">
+      <c r="X3" s="297" t="s">
         <v>43</v>
       </c>
-      <c r="Y3" s="300" t="s">
+      <c r="Y3" s="297" t="s">
         <v>44</v>
       </c>
-      <c r="Z3" s="300" t="s">
+      <c r="Z3" s="297" t="s">
         <v>45</v>
       </c>
-      <c r="AA3" s="300" t="s">
+      <c r="AA3" s="297" t="s">
         <v>46</v>
       </c>
-      <c r="AB3" s="300" t="s">
+      <c r="AB3" s="297" t="s">
         <v>47</v>
       </c>
-      <c r="AC3" s="300" t="s">
+      <c r="AC3" s="297" t="s">
         <v>48</v>
       </c>
-      <c r="AD3" s="300" t="s">
+      <c r="AD3" s="297" t="s">
         <v>49</v>
       </c>
-      <c r="AE3" s="300" t="s">
+      <c r="AE3" s="297" t="s">
         <v>50</v>
       </c>
-      <c r="AF3" s="300" t="s">
+      <c r="AF3" s="297" t="s">
         <v>51</v>
       </c>
-      <c r="AG3" s="300" t="s">
+      <c r="AG3" s="297" t="s">
         <v>52</v>
       </c>
-      <c r="AH3" s="300" t="s">
+      <c r="AH3" s="297" t="s">
         <v>53</v>
       </c>
-      <c r="AI3" s="300" t="s">
+      <c r="AI3" s="297" t="s">
         <v>54</v>
       </c>
-      <c r="AJ3" s="301" t="s">
+      <c r="AJ3" s="313" t="s">
         <v>55</v>
       </c>
       <c r="AK3" s="284" t="s">
         <v>56</v>
       </c>
-      <c r="AL3" s="300" t="s">
+      <c r="AL3" s="297" t="s">
         <v>57</v>
       </c>
       <c r="AM3" s="284" t="s">
@@ -8051,105 +8051,105 @@
       <c r="AN3" s="284" t="s">
         <v>59</v>
       </c>
-      <c r="AO3" s="296"/>
-      <c r="AP3" s="296"/>
-      <c r="AQ3" s="296"/>
-      <c r="AR3" s="296"/>
-      <c r="AS3" s="296"/>
-      <c r="AT3" s="296"/>
-      <c r="AU3" s="296"/>
-      <c r="AV3" s="296"/>
-      <c r="AW3" s="296"/>
+      <c r="AO3" s="285"/>
+      <c r="AP3" s="285"/>
+      <c r="AQ3" s="285"/>
+      <c r="AR3" s="285"/>
+      <c r="AS3" s="285"/>
+      <c r="AT3" s="285"/>
+      <c r="AU3" s="285"/>
+      <c r="AV3" s="285"/>
+      <c r="AW3" s="285"/>
       <c r="AX3" s="284" t="s">
         <v>21</v>
       </c>
-      <c r="AY3" s="297"/>
-      <c r="AZ3" s="297"/>
-      <c r="BA3" s="297"/>
-      <c r="BB3" s="297"/>
-      <c r="BC3" s="297"/>
-      <c r="BD3" s="297"/>
-      <c r="BE3" s="297"/>
-      <c r="BF3" s="297"/>
-      <c r="BG3" s="297"/>
-      <c r="BH3" s="297"/>
-      <c r="BI3" s="297"/>
-      <c r="BJ3" s="297"/>
-      <c r="BK3" s="298"/>
+      <c r="AY3" s="291"/>
+      <c r="AZ3" s="291"/>
+      <c r="BA3" s="291"/>
+      <c r="BB3" s="291"/>
+      <c r="BC3" s="291"/>
+      <c r="BD3" s="291"/>
+      <c r="BE3" s="291"/>
+      <c r="BF3" s="291"/>
+      <c r="BG3" s="291"/>
+      <c r="BH3" s="291"/>
+      <c r="BI3" s="291"/>
+      <c r="BJ3" s="291"/>
+      <c r="BK3" s="292"/>
       <c r="BL3" s="284" t="s">
         <v>60</v>
       </c>
-      <c r="BM3" s="297"/>
-      <c r="BN3" s="297"/>
-      <c r="BO3" s="297"/>
-      <c r="BP3" s="298"/>
-      <c r="BQ3" s="293" t="s">
+      <c r="BM3" s="291"/>
+      <c r="BN3" s="291"/>
+      <c r="BO3" s="291"/>
+      <c r="BP3" s="292"/>
+      <c r="BQ3" s="322" t="s">
         <v>61</v>
       </c>
-      <c r="BR3" s="293" t="s">
+      <c r="BR3" s="322" t="s">
         <v>62</v>
       </c>
-      <c r="BS3" s="293"/>
-      <c r="BT3" s="290"/>
-      <c r="BU3" s="287"/>
-      <c r="BV3" s="311"/>
-      <c r="BW3" s="312"/>
-      <c r="BX3" s="312"/>
-      <c r="BY3" s="313"/>
-      <c r="BZ3" s="318"/>
-      <c r="CA3" s="318"/>
-      <c r="CB3" s="318"/>
+      <c r="BS3" s="322"/>
+      <c r="BT3" s="320"/>
+      <c r="BU3" s="317"/>
+      <c r="BV3" s="301"/>
+      <c r="BW3" s="302"/>
+      <c r="BX3" s="302"/>
+      <c r="BY3" s="303"/>
+      <c r="BZ3" s="308"/>
+      <c r="CA3" s="308"/>
+      <c r="CB3" s="308"/>
     </row>
     <row r="4" spans="1:85" s="3" customFormat="1" ht="14" outlineLevel="1">
-      <c r="A4" s="296"/>
-      <c r="B4" s="296"/>
-      <c r="C4" s="296"/>
-      <c r="D4" s="296"/>
-      <c r="E4" s="296"/>
-      <c r="F4" s="296"/>
-      <c r="G4" s="296"/>
-      <c r="H4" s="296"/>
-      <c r="I4" s="296"/>
-      <c r="J4" s="296"/>
-      <c r="K4" s="296"/>
-      <c r="L4" s="296"/>
-      <c r="M4" s="296"/>
-      <c r="N4" s="296"/>
-      <c r="O4" s="296"/>
-      <c r="P4" s="296"/>
-      <c r="Q4" s="296"/>
-      <c r="R4" s="296"/>
-      <c r="S4" s="296"/>
-      <c r="T4" s="296"/>
-      <c r="U4" s="303"/>
-      <c r="V4" s="307"/>
-      <c r="W4" s="296"/>
-      <c r="X4" s="296"/>
-      <c r="Y4" s="296"/>
-      <c r="Z4" s="296"/>
-      <c r="AA4" s="296"/>
-      <c r="AB4" s="296"/>
-      <c r="AC4" s="296"/>
-      <c r="AD4" s="296"/>
-      <c r="AE4" s="296"/>
-      <c r="AF4" s="296"/>
-      <c r="AG4" s="296"/>
-      <c r="AH4" s="296"/>
-      <c r="AI4" s="296"/>
-      <c r="AJ4" s="302"/>
-      <c r="AK4" s="296"/>
-      <c r="AL4" s="296"/>
-      <c r="AM4" s="296"/>
-      <c r="AN4" s="296"/>
-      <c r="AO4" s="296"/>
-      <c r="AP4" s="296"/>
-      <c r="AQ4" s="296"/>
-      <c r="AR4" s="296"/>
-      <c r="AS4" s="296"/>
-      <c r="AT4" s="296"/>
-      <c r="AU4" s="296"/>
-      <c r="AV4" s="296"/>
-      <c r="AW4" s="296"/>
+      <c r="A4" s="285"/>
+      <c r="B4" s="285"/>
+      <c r="C4" s="285"/>
+      <c r="D4" s="285"/>
+      <c r="E4" s="285"/>
+      <c r="F4" s="285"/>
+      <c r="G4" s="285"/>
+      <c r="H4" s="285"/>
+      <c r="I4" s="285"/>
+      <c r="J4" s="285"/>
+      <c r="K4" s="285"/>
+      <c r="L4" s="285"/>
+      <c r="M4" s="285"/>
+      <c r="N4" s="285"/>
+      <c r="O4" s="285"/>
+      <c r="P4" s="285"/>
+      <c r="Q4" s="285"/>
+      <c r="R4" s="285"/>
+      <c r="S4" s="285"/>
+      <c r="T4" s="285"/>
+      <c r="U4" s="311"/>
+      <c r="V4" s="312"/>
+      <c r="W4" s="285"/>
+      <c r="X4" s="285"/>
+      <c r="Y4" s="285"/>
+      <c r="Z4" s="285"/>
+      <c r="AA4" s="285"/>
+      <c r="AB4" s="285"/>
+      <c r="AC4" s="285"/>
+      <c r="AD4" s="285"/>
+      <c r="AE4" s="285"/>
+      <c r="AF4" s="285"/>
+      <c r="AG4" s="285"/>
+      <c r="AH4" s="285"/>
+      <c r="AI4" s="285"/>
+      <c r="AJ4" s="314"/>
+      <c r="AK4" s="285"/>
+      <c r="AL4" s="285"/>
+      <c r="AM4" s="285"/>
+      <c r="AN4" s="285"/>
+      <c r="AO4" s="285"/>
+      <c r="AP4" s="285"/>
+      <c r="AQ4" s="285"/>
+      <c r="AR4" s="285"/>
+      <c r="AS4" s="285"/>
+      <c r="AT4" s="285"/>
+      <c r="AU4" s="285"/>
+      <c r="AV4" s="285"/>
+      <c r="AW4" s="285"/>
       <c r="AX4" s="244" t="s">
         <v>63</v>
       </c>
@@ -8159,46 +8159,46 @@
       <c r="AZ4" s="244" t="s">
         <v>65</v>
       </c>
-      <c r="BA4" s="299" t="s">
+      <c r="BA4" s="315" t="s">
         <v>66</v>
       </c>
-      <c r="BB4" s="295" t="s">
+      <c r="BB4" s="296" t="s">
         <v>67</v>
       </c>
-      <c r="BC4" s="295" t="s">
+      <c r="BC4" s="296" t="s">
         <v>68</v>
       </c>
-      <c r="BD4" s="295" t="s">
+      <c r="BD4" s="296" t="s">
         <v>69</v>
       </c>
-      <c r="BE4" s="295" t="s">
+      <c r="BE4" s="296" t="s">
         <v>70</v>
       </c>
-      <c r="BF4" s="295" t="s">
+      <c r="BF4" s="296" t="s">
         <v>71</v>
       </c>
-      <c r="BG4" s="295" t="s">
+      <c r="BG4" s="296" t="s">
         <v>72</v>
       </c>
-      <c r="BH4" s="295" t="s">
+      <c r="BH4" s="296" t="s">
         <v>73</v>
       </c>
-      <c r="BI4" s="295" t="s">
+      <c r="BI4" s="296" t="s">
         <v>74</v>
       </c>
-      <c r="BJ4" s="295" t="s">
+      <c r="BJ4" s="296" t="s">
         <v>75</v>
       </c>
       <c r="BK4" s="284" t="s">
         <v>76</v>
       </c>
-      <c r="BL4" s="295" t="s">
+      <c r="BL4" s="296" t="s">
         <v>77</v>
       </c>
       <c r="BM4" s="284" t="s">
         <v>78</v>
       </c>
-      <c r="BN4" s="295" t="s">
+      <c r="BN4" s="296" t="s">
         <v>79</v>
       </c>
       <c r="BO4" s="284" t="s">
@@ -8207,73 +8207,73 @@
       <c r="BP4" s="284" t="s">
         <v>81</v>
       </c>
-      <c r="BQ4" s="293"/>
-      <c r="BR4" s="293"/>
-      <c r="BS4" s="293"/>
-      <c r="BT4" s="290"/>
-      <c r="BU4" s="287"/>
-      <c r="BV4" s="314"/>
-      <c r="BW4" s="315"/>
-      <c r="BX4" s="315"/>
-      <c r="BY4" s="316"/>
-      <c r="BZ4" s="318"/>
-      <c r="CA4" s="318"/>
-      <c r="CB4" s="318"/>
+      <c r="BQ4" s="322"/>
+      <c r="BR4" s="322"/>
+      <c r="BS4" s="322"/>
+      <c r="BT4" s="320"/>
+      <c r="BU4" s="317"/>
+      <c r="BV4" s="304"/>
+      <c r="BW4" s="305"/>
+      <c r="BX4" s="305"/>
+      <c r="BY4" s="306"/>
+      <c r="BZ4" s="308"/>
+      <c r="CA4" s="308"/>
+      <c r="CB4" s="308"/>
     </row>
     <row r="5" spans="1:85" s="3" customFormat="1" ht="42" outlineLevel="1">
-      <c r="A5" s="285"/>
-      <c r="B5" s="285"/>
-      <c r="C5" s="285"/>
-      <c r="D5" s="285"/>
-      <c r="E5" s="285"/>
-      <c r="F5" s="285"/>
-      <c r="G5" s="285"/>
-      <c r="H5" s="285"/>
-      <c r="I5" s="285"/>
-      <c r="J5" s="285"/>
-      <c r="K5" s="285"/>
-      <c r="L5" s="285"/>
-      <c r="M5" s="285"/>
-      <c r="N5" s="285"/>
-      <c r="O5" s="285"/>
-      <c r="P5" s="285"/>
-      <c r="Q5" s="285"/>
-      <c r="R5" s="285"/>
-      <c r="S5" s="285"/>
-      <c r="T5" s="285"/>
+      <c r="A5" s="286"/>
+      <c r="B5" s="286"/>
+      <c r="C5" s="286"/>
+      <c r="D5" s="286"/>
+      <c r="E5" s="286"/>
+      <c r="F5" s="286"/>
+      <c r="G5" s="286"/>
+      <c r="H5" s="286"/>
+      <c r="I5" s="286"/>
+      <c r="J5" s="286"/>
+      <c r="K5" s="286"/>
+      <c r="L5" s="286"/>
+      <c r="M5" s="286"/>
+      <c r="N5" s="286"/>
+      <c r="O5" s="286"/>
+      <c r="P5" s="286"/>
+      <c r="Q5" s="286"/>
+      <c r="R5" s="286"/>
+      <c r="S5" s="286"/>
+      <c r="T5" s="286"/>
       <c r="U5" s="254" t="s">
         <v>82</v>
       </c>
       <c r="V5" s="254" t="s">
         <v>83</v>
       </c>
-      <c r="W5" s="285"/>
-      <c r="X5" s="285"/>
-      <c r="Y5" s="285"/>
-      <c r="Z5" s="285"/>
-      <c r="AA5" s="285"/>
-      <c r="AB5" s="285"/>
-      <c r="AC5" s="285"/>
-      <c r="AD5" s="285"/>
-      <c r="AE5" s="285"/>
-      <c r="AF5" s="285"/>
-      <c r="AG5" s="285"/>
-      <c r="AH5" s="285"/>
-      <c r="AI5" s="285"/>
-      <c r="AJ5" s="303"/>
-      <c r="AK5" s="285"/>
-      <c r="AL5" s="285"/>
-      <c r="AM5" s="285"/>
-      <c r="AN5" s="285"/>
-      <c r="AO5" s="285"/>
-      <c r="AP5" s="285"/>
-      <c r="AQ5" s="285"/>
-      <c r="AR5" s="285"/>
-      <c r="AS5" s="285"/>
-      <c r="AT5" s="285"/>
-      <c r="AU5" s="285"/>
-      <c r="AV5" s="285"/>
-      <c r="AW5" s="285"/>
+      <c r="W5" s="286"/>
+      <c r="X5" s="286"/>
+      <c r="Y5" s="286"/>
+      <c r="Z5" s="286"/>
+      <c r="AA5" s="286"/>
+      <c r="AB5" s="286"/>
+      <c r="AC5" s="286"/>
+      <c r="AD5" s="286"/>
+      <c r="AE5" s="286"/>
+      <c r="AF5" s="286"/>
+      <c r="AG5" s="286"/>
+      <c r="AH5" s="286"/>
+      <c r="AI5" s="286"/>
+      <c r="AJ5" s="311"/>
+      <c r="AK5" s="286"/>
+      <c r="AL5" s="286"/>
+      <c r="AM5" s="286"/>
+      <c r="AN5" s="286"/>
+      <c r="AO5" s="286"/>
+      <c r="AP5" s="286"/>
+      <c r="AQ5" s="286"/>
+      <c r="AR5" s="286"/>
+      <c r="AS5" s="286"/>
+      <c r="AT5" s="286"/>
+      <c r="AU5" s="286"/>
+      <c r="AV5" s="286"/>
+      <c r="AW5" s="286"/>
       <c r="AX5" s="245" t="s">
         <v>84</v>
       </c>
@@ -8283,27 +8283,27 @@
       <c r="AZ5" s="245" t="s">
         <v>86</v>
       </c>
-      <c r="BA5" s="285"/>
-      <c r="BB5" s="285"/>
-      <c r="BC5" s="285"/>
-      <c r="BD5" s="285"/>
-      <c r="BE5" s="285"/>
-      <c r="BF5" s="285"/>
-      <c r="BG5" s="285"/>
-      <c r="BH5" s="285"/>
-      <c r="BI5" s="285"/>
-      <c r="BJ5" s="285"/>
-      <c r="BK5" s="285"/>
-      <c r="BL5" s="285"/>
-      <c r="BM5" s="285"/>
-      <c r="BN5" s="285"/>
-      <c r="BO5" s="285"/>
-      <c r="BP5" s="285"/>
-      <c r="BQ5" s="294"/>
-      <c r="BR5" s="294"/>
-      <c r="BS5" s="294"/>
-      <c r="BT5" s="291"/>
-      <c r="BU5" s="288"/>
+      <c r="BA5" s="286"/>
+      <c r="BB5" s="286"/>
+      <c r="BC5" s="286"/>
+      <c r="BD5" s="286"/>
+      <c r="BE5" s="286"/>
+      <c r="BF5" s="286"/>
+      <c r="BG5" s="286"/>
+      <c r="BH5" s="286"/>
+      <c r="BI5" s="286"/>
+      <c r="BJ5" s="286"/>
+      <c r="BK5" s="286"/>
+      <c r="BL5" s="286"/>
+      <c r="BM5" s="286"/>
+      <c r="BN5" s="286"/>
+      <c r="BO5" s="286"/>
+      <c r="BP5" s="286"/>
+      <c r="BQ5" s="323"/>
+      <c r="BR5" s="323"/>
+      <c r="BS5" s="323"/>
+      <c r="BT5" s="321"/>
+      <c r="BU5" s="318"/>
       <c r="BV5" s="255" t="s">
         <v>87</v>
       </c>
@@ -8316,9 +8316,9 @@
       <c r="BY5" s="256" t="s">
         <v>90</v>
       </c>
-      <c r="BZ5" s="319"/>
-      <c r="CA5" s="319"/>
-      <c r="CB5" s="319"/>
+      <c r="BZ5" s="309"/>
+      <c r="CA5" s="309"/>
+      <c r="CB5" s="309"/>
     </row>
     <row r="6" spans="1:85" s="250" customFormat="1" ht="19.25" customHeight="1">
       <c r="A6" s="258">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="H6" s="81">
         <f t="shared" ref="H6:H12" si="1">BZ6-BX6-F6-G6</f>
-        <v>50480000</v>
+        <v>53480000</v>
       </c>
       <c r="I6" s="79">
         <v>1</v>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="AN6" s="81">
         <f t="shared" ref="AN6:AN12" si="6">IF(E6="LN",H6*(J6+K6)/26+(G6+H6)*50%*L6/26+MAX($F6*O6/26*150%,O6*$BU6/26)-AB6+MAX($F6*P6/26*200%,P6*$BU6/26)-AC6+MAX($F6*Q6/26*300%,Q6*$BU6/26)-AD6+BU6*R6/26-AE6+AG6-AF6,H6-H6*($CA$1-J6-K6)/26+(G6+H6)*50%*L6/26+BU6*N6/26-AA6+MAX($F6*O6/26*150%,O6*$BU6/26)-AB6+MAX($F6*P6/26*200%,P6*$BU6/26)-AC6+MAX($F6*Q6/26*300%,Q6*$BU6/26)-AD6+BU6*R6/26-AE6+AG6-AF6+(F6-F6*($CA$1-J6-K6)/26-X6)+(G6-G6*($CA$1-J6-K6)/26-AM6))</f>
-        <v>50480000</v>
+        <v>53480000</v>
       </c>
       <c r="AO6" s="81"/>
       <c r="AP6" s="81"/>
@@ -8462,7 +8462,7 @@
       <c r="AT6" s="81"/>
       <c r="AU6" s="81">
         <f>X6+Y6+Z6+AA6+AB6+AC6+AD6+AE6+AF6+AH6+AI6+AJ6+AK6+AL6+AM6+AN6+AO6-AP6+AQ6+AR6+AS6+AT6</f>
-        <v>61000000</v>
+        <v>64000000</v>
       </c>
       <c r="AV6" s="81"/>
       <c r="AW6" s="81" t="s">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="BF6" s="263">
         <f>AU6-BE6+AV6</f>
-        <v>60270000</v>
+        <v>63270000</v>
       </c>
       <c r="BG6" s="263">
         <v>3</v>
@@ -8510,11 +8510,11 @@
       </c>
       <c r="BJ6" s="263">
         <f>BF6-BA6-BB6+BC6-BG6*BH6-BI6</f>
-        <v>25170400</v>
+        <v>28170400</v>
       </c>
       <c r="BK6" s="264">
         <f>IF(D6="TV",BJ6*10%,IF(BJ6&gt;0,ROUND(IF(BJ6&gt;=80000000,BJ6*35%-9850000,IF(BJ6&gt;=52000000,BJ6*30%-5850000,IF(BJ6&gt;=32000000,BJ6*25%-3250000,IF(BJ6&gt;=18000000,BJ6*20%-1650000,IF(BJ6&gt;=10000000,BJ6*15%-750000,IF(BJ6&gt;5000000,BJ6*10%-250000,BJ6*5%)))))),0),0))</f>
-        <v>3384080</v>
+        <v>3984080</v>
       </c>
       <c r="BL6" s="263"/>
       <c r="BM6" s="263"/>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="BT6" s="265">
         <f t="shared" ref="BT6:BT12" si="8">AU6-BA6-BB6+BC6-BD6-BK6-BL6-BM6-BN6-BO6-BP6-BQ6+BR6-BS6</f>
-        <v>30674966.153846148</v>
+        <v>33074966.153846148</v>
       </c>
       <c r="BU6" s="266">
         <v>60000000</v>
@@ -8543,11 +8543,12 @@
         <v>200000</v>
       </c>
       <c r="BY6" s="264">
-        <v>0</v>
+        <f t="shared" ref="BY6:BY12" si="9">+BU6*5%</f>
+        <v>3000000</v>
       </c>
       <c r="BZ6" s="264">
         <f>SUM(BU6:BY6)</f>
-        <v>60200000</v>
+        <v>63200000</v>
       </c>
       <c r="CA6" s="264"/>
       <c r="CB6" s="264"/>
@@ -8629,27 +8630,27 @@
         <v>7827692.307692308</v>
       </c>
       <c r="Y7" s="81">
-        <f t="shared" ref="Y7:Y12" si="9">L7*F7/26</f>
+        <f t="shared" ref="Y7:Y12" si="10">L7*F7/26</f>
         <v>0</v>
       </c>
       <c r="Z7" s="81">
-        <f t="shared" ref="Z7:Z12" si="10">F7*M7/26</f>
+        <f t="shared" ref="Z7:Z12" si="11">F7*M7/26</f>
         <v>0</v>
       </c>
       <c r="AA7" s="81">
-        <f t="shared" ref="AA7:AA12" si="11">F7*N7/26</f>
+        <f t="shared" ref="AA7:AA12" si="12">F7*N7/26</f>
         <v>0</v>
       </c>
       <c r="AB7" s="81">
-        <f t="shared" ref="AB7:AB12" si="12">F7*O7*150%/26</f>
+        <f t="shared" ref="AB7:AB12" si="13">F7*O7*150%/26</f>
         <v>0</v>
       </c>
       <c r="AC7" s="81">
-        <f t="shared" ref="AC7:AC12" si="13">F7*P7/26*200%</f>
+        <f t="shared" ref="AC7:AC12" si="14">F7*P7/26*200%</f>
         <v>0</v>
       </c>
       <c r="AD7" s="81">
-        <f t="shared" ref="AD7:AD12" si="14">F7*Q7/26*300%</f>
+        <f t="shared" ref="AD7:AD12" si="15">F7*Q7/26*300%</f>
         <v>0</v>
       </c>
       <c r="AE7" s="81">
@@ -8657,7 +8658,7 @@
         <v>0</v>
       </c>
       <c r="AF7" s="81">
-        <f t="shared" ref="AF7:AF12" si="15">S7*F7/26/8</f>
+        <f t="shared" ref="AF7:AF12" si="16">S7*F7/26/8</f>
         <v>0</v>
       </c>
       <c r="AG7" s="81">
@@ -8665,7 +8666,7 @@
         <v>0</v>
       </c>
       <c r="AH7" s="81">
-        <f t="shared" ref="AH7:AH12" si="16">F7*U7/26</f>
+        <f t="shared" ref="AH7:AH12" si="17">F7*U7/26</f>
         <v>0</v>
       </c>
       <c r="AI7" s="81"/>
@@ -8679,7 +8680,7 @@
         <v>0</v>
       </c>
       <c r="AM7" s="81">
-        <f t="shared" ref="AM7:AM12" si="17">G7/26*J7</f>
+        <f t="shared" ref="AM7:AM12" si="18">G7/26*J7</f>
         <v>0</v>
       </c>
       <c r="AN7" s="81">
@@ -8695,12 +8696,12 @@
       <c r="AS7" s="81"/>
       <c r="AT7" s="81"/>
       <c r="AU7" s="81">
-        <f t="shared" ref="AU7:AU12" si="18">X7+Y7+Z7+AA7+AB7+AC7+AD7+AE7+AF7+AH7+AI7+AJ7+AK7+AL7+AM7+AN7+AO7-AP7+AQ7+AR7+AS7+AT7</f>
+        <f t="shared" ref="AU7:AU12" si="19">X7+Y7+Z7+AA7+AB7+AC7+AD7+AE7+AF7+AH7+AI7+AJ7+AK7+AL7+AM7+AN7+AO7-AP7+AQ7+AR7+AS7+AT7</f>
         <v>48758461.538461544</v>
       </c>
       <c r="AV7" s="81"/>
       <c r="AW7" s="81" t="str">
-        <f t="shared" ref="AW7:AW12" si="19">IF(D7="CT","x",0)</f>
+        <f t="shared" ref="AW7:AW12" si="20">IF(D7="CT","x",0)</f>
         <v>x</v>
       </c>
       <c r="AX7" s="263">
@@ -8722,15 +8723,15 @@
       <c r="BB7" s="263"/>
       <c r="BC7" s="263"/>
       <c r="BD7" s="263">
-        <f t="shared" ref="BD7:BD12" si="20">IF(F7*1%&gt;=234000,234000,F7*1%)</f>
+        <f t="shared" ref="BD7:BD12" si="21">IF(F7*1%&gt;=234000,234000,F7*1%)</f>
         <v>84800</v>
       </c>
       <c r="BE7" s="263">
-        <f t="shared" ref="BE7:BE12" si="21">AL7+IF(D7="CT",IF(AQ7&gt;=730000,730000,AQ7),0)+IF(((AU7-AL7-IF(AQ7&gt;=730000,730000,AQ7)-AR7)*15%-AR7)&gt;"0",((AU7-AL7-IF(AQ7&gt;=730000,730000,AQ7)-AR7)*15%-AR7),0)</f>
+        <f t="shared" ref="BE7:BE12" si="22">AL7+IF(D7="CT",IF(AQ7&gt;=730000,730000,AQ7),0)+IF(((AU7-AL7-IF(AQ7&gt;=730000,730000,AQ7)-AR7)*15%-AR7)&gt;"0",((AU7-AL7-IF(AQ7&gt;=730000,730000,AQ7)-AR7)*15%-AR7),0)</f>
         <v>720000</v>
       </c>
       <c r="BF7" s="263">
-        <f t="shared" ref="BF7:BF12" si="22">AU7-BE7+AV7</f>
+        <f t="shared" ref="BF7:BF12" si="23">AU7-BE7+AV7</f>
         <v>48038461.538461544</v>
       </c>
       <c r="BG7" s="263"/>
@@ -8738,15 +8739,15 @@
         <v>6200000</v>
       </c>
       <c r="BI7" s="263">
-        <f t="shared" ref="BI7:BI12" si="23">IF(D7="CT",15500000,0)</f>
+        <f t="shared" ref="BI7:BI12" si="24">IF(D7="CT",15500000,0)</f>
         <v>15500000</v>
       </c>
       <c r="BJ7" s="263">
-        <f t="shared" ref="BJ7:BJ12" si="24">BF7-BA7-BB7+BC7-BG7*BH7-BI7</f>
+        <f t="shared" ref="BJ7:BJ12" si="25">BF7-BA7-BB7+BC7-BG7*BH7-BI7</f>
         <v>31648061.538461544</v>
       </c>
       <c r="BK7" s="264">
-        <f t="shared" ref="BK7:BK12" si="25">IF(D7="TV",BJ7*10%,IF(BJ7&gt;0,ROUND(IF(BJ7&gt;=80000000,BJ7*35%-9850000,IF(BJ7&gt;=52000000,BJ7*30%-5850000,IF(BJ7&gt;=32000000,BJ7*25%-3250000,IF(BJ7&gt;=18000000,BJ7*20%-1650000,IF(BJ7&gt;=10000000,BJ7*15%-750000,IF(BJ7&gt;5000000,BJ7*10%-250000,BJ7*5%)))))),0),0))</f>
+        <f t="shared" ref="BK7:BK12" si="26">IF(D7="TV",BJ7*10%,IF(BJ7&gt;0,ROUND(IF(BJ7&gt;=80000000,BJ7*35%-9850000,IF(BJ7&gt;=52000000,BJ7*30%-5850000,IF(BJ7&gt;=32000000,BJ7*25%-3250000,IF(BJ7&gt;=18000000,BJ7*20%-1650000,IF(BJ7&gt;=10000000,BJ7*15%-750000,IF(BJ7&gt;5000000,BJ7*10%-250000,BJ7*5%)))))),0),0))</f>
         <v>4679612</v>
       </c>
       <c r="BL7" s="263"/>
@@ -8778,7 +8779,7 @@
         <v>200000</v>
       </c>
       <c r="BY7" s="264">
-        <f t="shared" ref="BY7:BY12" si="26">+BU7*5%</f>
+        <f t="shared" si="9"/>
         <v>2000000</v>
       </c>
       <c r="BZ7" s="264">
@@ -8865,27 +8866,27 @@
         <v>7218461.538461538</v>
       </c>
       <c r="Y8" s="81">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="Z8" s="81">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AA8" s="81">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AB8" s="81">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AC8" s="81">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AD8" s="81">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE8" s="81">
@@ -8893,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="AF8" s="81">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AG8" s="81">
@@ -8901,7 +8902,7 @@
         <v>3246153.846153846</v>
       </c>
       <c r="AH8" s="81">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI8" s="81"/>
@@ -8915,7 +8916,7 @@
         <v>0</v>
       </c>
       <c r="AM8" s="81">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AN8" s="81">
@@ -8931,12 +8932,12 @@
       <c r="AS8" s="81"/>
       <c r="AT8" s="81"/>
       <c r="AU8" s="81">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>42575384.615384616</v>
       </c>
       <c r="AV8" s="81"/>
       <c r="AW8" s="81" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>x</v>
       </c>
       <c r="AX8" s="263">
@@ -8958,15 +8959,15 @@
       <c r="BB8" s="263"/>
       <c r="BC8" s="263"/>
       <c r="BD8" s="263">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>78200</v>
       </c>
       <c r="BE8" s="263">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>560000</v>
       </c>
       <c r="BF8" s="263">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>42015384.615384616</v>
       </c>
       <c r="BG8" s="263"/>
@@ -8974,15 +8975,15 @@
         <v>6200000</v>
       </c>
       <c r="BI8" s="263">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>15500000</v>
       </c>
       <c r="BJ8" s="263">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>25694284.615384616</v>
       </c>
       <c r="BK8" s="264">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>3488857</v>
       </c>
       <c r="BL8" s="263"/>
@@ -9014,7 +9015,7 @@
         <v>200000</v>
       </c>
       <c r="BY8" s="264">
-        <f t="shared" si="26"/>
+        <f t="shared" si="9"/>
         <v>2000000</v>
       </c>
       <c r="BZ8" s="264">
@@ -9101,27 +9102,27 @@
         <v>6990000</v>
       </c>
       <c r="Y9" s="81">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="Z9" s="81">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AA9" s="81">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AB9" s="81">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AC9" s="81">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AD9" s="81">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE9" s="81">
@@ -9129,7 +9130,7 @@
         <v>0</v>
       </c>
       <c r="AF9" s="81">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AG9" s="81">
@@ -9137,7 +9138,7 @@
         <v>0</v>
       </c>
       <c r="AH9" s="81">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI9" s="81"/>
@@ -9151,7 +9152,7 @@
         <v>0</v>
       </c>
       <c r="AM9" s="81">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AN9" s="81">
@@ -9167,12 +9168,12 @@
       <c r="AS9" s="81"/>
       <c r="AT9" s="81"/>
       <c r="AU9" s="81">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>26893076.923076924</v>
       </c>
       <c r="AV9" s="81"/>
       <c r="AW9" s="81" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>x</v>
       </c>
       <c r="AX9" s="263">
@@ -9194,15 +9195,15 @@
       <c r="BB9" s="263"/>
       <c r="BC9" s="263"/>
       <c r="BD9" s="263">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>69900</v>
       </c>
       <c r="BE9" s="263">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>720000</v>
       </c>
       <c r="BF9" s="263">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>26173076.923076924</v>
       </c>
       <c r="BG9" s="263"/>
@@ -9210,15 +9211,15 @@
         <v>6200000</v>
       </c>
       <c r="BI9" s="263">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>15500000</v>
       </c>
       <c r="BJ9" s="263">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>9939126.9230769239</v>
       </c>
       <c r="BK9" s="264">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>743913</v>
       </c>
       <c r="BL9" s="263"/>
@@ -9250,7 +9251,7 @@
         <v>200000</v>
       </c>
       <c r="BY9" s="264">
-        <f t="shared" si="26"/>
+        <f t="shared" si="9"/>
         <v>1150000</v>
       </c>
       <c r="BZ9" s="264">
@@ -9339,27 +9340,27 @@
         <v>4103846.153846154</v>
       </c>
       <c r="Y10" s="81">
-        <f t="shared" si="9"/>
-        <v>373076.92307692306</v>
-      </c>
-      <c r="Z10" s="81">
         <f t="shared" si="10"/>
         <v>373076.92307692306</v>
       </c>
+      <c r="Z10" s="81">
+        <f t="shared" si="11"/>
+        <v>373076.92307692306</v>
+      </c>
       <c r="AA10" s="81">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AB10" s="81">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AC10" s="81">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AD10" s="81">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE10" s="81">
@@ -9367,7 +9368,7 @@
         <v>111923.07692307692</v>
       </c>
       <c r="AF10" s="81">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AG10" s="81">
@@ -9375,7 +9376,7 @@
         <v>0</v>
       </c>
       <c r="AH10" s="81">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI10" s="81"/>
@@ -9389,7 +9390,7 @@
         <v>0</v>
       </c>
       <c r="AM10" s="81">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AN10" s="81">
@@ -9405,12 +9406,12 @@
       <c r="AS10" s="81"/>
       <c r="AT10" s="81"/>
       <c r="AU10" s="81">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>12183076.923076924</v>
       </c>
       <c r="AV10" s="81"/>
       <c r="AW10" s="81" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>x</v>
       </c>
       <c r="AX10" s="263">
@@ -9432,15 +9433,15 @@
       <c r="BB10" s="263"/>
       <c r="BC10" s="263"/>
       <c r="BD10" s="263">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>48500</v>
       </c>
       <c r="BE10" s="263">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>560000</v>
       </c>
       <c r="BF10" s="263">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11623076.923076924</v>
       </c>
       <c r="BG10" s="263"/>
@@ -9448,15 +9449,15 @@
         <v>6200000</v>
       </c>
       <c r="BI10" s="263">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>15500000</v>
       </c>
       <c r="BJ10" s="263">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-4386173.0769230761</v>
       </c>
       <c r="BK10" s="264">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BL10" s="263"/>
@@ -9488,7 +9489,7 @@
         <v>200000</v>
       </c>
       <c r="BY10" s="264">
-        <f t="shared" si="26"/>
+        <f t="shared" si="9"/>
         <v>550000</v>
       </c>
       <c r="BZ10" s="264">
@@ -9578,27 +9579,27 @@
         <v>6340000</v>
       </c>
       <c r="Y11" s="81">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="Z11" s="81">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AA11" s="81">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AB11" s="81">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AC11" s="81">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AD11" s="81">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE11" s="81">
@@ -9606,7 +9607,7 @@
         <v>0</v>
       </c>
       <c r="AF11" s="81">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AG11" s="81">
@@ -9614,7 +9615,7 @@
         <v>0</v>
       </c>
       <c r="AH11" s="81">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI11" s="81"/>
@@ -9628,7 +9629,7 @@
         <v>0</v>
       </c>
       <c r="AM11" s="81">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>780000</v>
       </c>
       <c r="AN11" s="81">
@@ -9644,12 +9645,12 @@
       <c r="AS11" s="81"/>
       <c r="AT11" s="81"/>
       <c r="AU11" s="81">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>24870000</v>
       </c>
       <c r="AV11" s="81"/>
       <c r="AW11" s="81">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AX11" s="263">
@@ -9671,15 +9672,15 @@
       <c r="BB11" s="263"/>
       <c r="BC11" s="263"/>
       <c r="BD11" s="263">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>63400</v>
       </c>
       <c r="BE11" s="263">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BF11" s="263">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>24870000</v>
       </c>
       <c r="BG11" s="263"/>
@@ -9687,15 +9688,15 @@
         <v>6200000</v>
       </c>
       <c r="BI11" s="263">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BJ11" s="263">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>24870000</v>
       </c>
       <c r="BK11" s="264">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>2487000</v>
       </c>
       <c r="BL11" s="263"/>
@@ -9727,7 +9728,7 @@
         <v>200000</v>
       </c>
       <c r="BY11" s="264">
-        <f t="shared" si="26"/>
+        <f t="shared" si="9"/>
         <v>1150000</v>
       </c>
       <c r="BZ11" s="264">
@@ -9819,27 +9820,27 @@
         <v>6340000</v>
       </c>
       <c r="Y12" s="81">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="Z12" s="81">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AA12" s="81">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AB12" s="81">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1828846.1538461538</v>
       </c>
       <c r="AC12" s="81">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>975384.61538461538</v>
       </c>
       <c r="AD12" s="81">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE12" s="81">
@@ -9847,7 +9848,7 @@
         <v>0</v>
       </c>
       <c r="AF12" s="81">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AG12" s="81">
@@ -9855,7 +9856,7 @@
         <v>0</v>
       </c>
       <c r="AH12" s="81">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI12" s="81"/>
@@ -9869,7 +9870,7 @@
         <v>0</v>
       </c>
       <c r="AM12" s="81">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>300000</v>
       </c>
       <c r="AN12" s="81">
@@ -9885,12 +9886,12 @@
       <c r="AS12" s="81"/>
       <c r="AT12" s="81"/>
       <c r="AU12" s="81">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>22986923.076923076</v>
       </c>
       <c r="AV12" s="81"/>
       <c r="AW12" s="81" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>x</v>
       </c>
       <c r="AX12" s="263">
@@ -9912,15 +9913,15 @@
       <c r="BB12" s="263"/>
       <c r="BC12" s="263"/>
       <c r="BD12" s="263">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>63400</v>
       </c>
       <c r="BE12" s="263">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>560000</v>
       </c>
       <c r="BF12" s="263">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>22426923.076923076</v>
       </c>
       <c r="BG12" s="263"/>
@@ -9928,15 +9929,15 @@
         <v>6200000</v>
       </c>
       <c r="BI12" s="263">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>15500000</v>
       </c>
       <c r="BJ12" s="263">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>6229723.0769230761</v>
       </c>
       <c r="BK12" s="264">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>372972</v>
       </c>
       <c r="BL12" s="263"/>
@@ -9968,7 +9969,7 @@
         <v>200000</v>
       </c>
       <c r="BY12" s="264">
-        <f t="shared" si="26"/>
+        <f t="shared" si="9"/>
         <v>850000</v>
       </c>
       <c r="BZ12" s="264">
@@ -10587,43 +10588,16 @@
     </row>
   </sheetData>
   <mergeCells count="79">
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="G2:G5"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="D2:D5"/>
-    <mergeCell ref="H2:H5"/>
-    <mergeCell ref="I2:I5"/>
-    <mergeCell ref="J2:W2"/>
-    <mergeCell ref="X2:AN2"/>
-    <mergeCell ref="AO2:AO5"/>
-    <mergeCell ref="P3:P5"/>
-    <mergeCell ref="Q3:Q5"/>
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="S3:S5"/>
-    <mergeCell ref="O3:O5"/>
-    <mergeCell ref="AW2:AW5"/>
-    <mergeCell ref="AX2:BP2"/>
-    <mergeCell ref="BQ2:BR2"/>
-    <mergeCell ref="BE4:BE5"/>
-    <mergeCell ref="BF4:BF5"/>
-    <mergeCell ref="BG4:BG5"/>
-    <mergeCell ref="BH4:BH5"/>
-    <mergeCell ref="AQ2:AQ5"/>
-    <mergeCell ref="AR2:AR5"/>
-    <mergeCell ref="AS2:AS5"/>
-    <mergeCell ref="AT2:AT5"/>
-    <mergeCell ref="AU2:AU5"/>
-    <mergeCell ref="AV2:AV5"/>
-    <mergeCell ref="AP2:AP5"/>
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="L3:L5"/>
-    <mergeCell ref="M3:M5"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="Z3:Z5"/>
+    <mergeCell ref="BU2:BU5"/>
+    <mergeCell ref="BT2:BT5"/>
+    <mergeCell ref="BS2:BS5"/>
+    <mergeCell ref="BR3:BR5"/>
+    <mergeCell ref="BQ3:BQ5"/>
+    <mergeCell ref="BK4:BK5"/>
+    <mergeCell ref="BL4:BL5"/>
+    <mergeCell ref="BM4:BM5"/>
+    <mergeCell ref="BO4:BO5"/>
+    <mergeCell ref="BP4:BP5"/>
     <mergeCell ref="BV2:BY4"/>
     <mergeCell ref="BZ2:BZ5"/>
     <mergeCell ref="CA2:CA5"/>
@@ -10640,14 +10614,34 @@
     <mergeCell ref="AD3:AD5"/>
     <mergeCell ref="AE3:AE5"/>
     <mergeCell ref="AF3:AF5"/>
+    <mergeCell ref="AV2:AV5"/>
+    <mergeCell ref="AP2:AP5"/>
+    <mergeCell ref="J3:J5"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="L3:L5"/>
+    <mergeCell ref="M3:M5"/>
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="Z3:Z5"/>
     <mergeCell ref="AG3:AG5"/>
     <mergeCell ref="AH3:AH5"/>
     <mergeCell ref="AI3:AI5"/>
     <mergeCell ref="AJ3:AJ5"/>
     <mergeCell ref="AK3:AK5"/>
-    <mergeCell ref="BN4:BN5"/>
     <mergeCell ref="AM3:AM5"/>
     <mergeCell ref="AN3:AN5"/>
+    <mergeCell ref="AQ2:AQ5"/>
+    <mergeCell ref="AR2:AR5"/>
+    <mergeCell ref="AS2:AS5"/>
+    <mergeCell ref="AT2:AT5"/>
+    <mergeCell ref="AU2:AU5"/>
+    <mergeCell ref="AW2:AW5"/>
+    <mergeCell ref="AX2:BP2"/>
+    <mergeCell ref="BQ2:BR2"/>
+    <mergeCell ref="BE4:BE5"/>
+    <mergeCell ref="BF4:BF5"/>
+    <mergeCell ref="BG4:BG5"/>
+    <mergeCell ref="BH4:BH5"/>
+    <mergeCell ref="BN4:BN5"/>
     <mergeCell ref="AX3:BK3"/>
     <mergeCell ref="BL3:BP3"/>
     <mergeCell ref="BA4:BA5"/>
@@ -10656,16 +10650,23 @@
     <mergeCell ref="BD4:BD5"/>
     <mergeCell ref="BI4:BI5"/>
     <mergeCell ref="BJ4:BJ5"/>
-    <mergeCell ref="BK4:BK5"/>
-    <mergeCell ref="BL4:BL5"/>
-    <mergeCell ref="BM4:BM5"/>
-    <mergeCell ref="BO4:BO5"/>
-    <mergeCell ref="BP4:BP5"/>
-    <mergeCell ref="BU2:BU5"/>
-    <mergeCell ref="BT2:BT5"/>
-    <mergeCell ref="BS2:BS5"/>
-    <mergeCell ref="BR3:BR5"/>
-    <mergeCell ref="BQ3:BQ5"/>
+    <mergeCell ref="H2:H5"/>
+    <mergeCell ref="I2:I5"/>
+    <mergeCell ref="J2:W2"/>
+    <mergeCell ref="X2:AN2"/>
+    <mergeCell ref="AO2:AO5"/>
+    <mergeCell ref="P3:P5"/>
+    <mergeCell ref="Q3:Q5"/>
+    <mergeCell ref="R3:R5"/>
+    <mergeCell ref="S3:S5"/>
+    <mergeCell ref="O3:O5"/>
+    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="G2:G5"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="D2:D5"/>
   </mergeCells>
   <conditionalFormatting sqref="A2:A5">
     <cfRule type="duplicateValues" dxfId="33" priority="1"/>
@@ -10873,91 +10874,91 @@
       <c r="CD2" s="235"/>
     </row>
     <row r="3" spans="1:87" s="236" customFormat="1" ht="12" customHeight="1" outlineLevel="1">
-      <c r="A3" s="359" t="str">
+      <c r="A3" s="324" t="str">
         <f ca="1">"BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …."&amp;" NĂM "&amp;YEAR(NOW())</f>
         <v>BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …. NĂM 2026</v>
       </c>
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
-      <c r="M3" s="359"/>
-      <c r="N3" s="359"/>
-      <c r="O3" s="359"/>
-      <c r="P3" s="359"/>
-      <c r="Q3" s="359"/>
-      <c r="R3" s="359"/>
-      <c r="S3" s="359"/>
-      <c r="T3" s="359"/>
-      <c r="U3" s="359"/>
-      <c r="V3" s="359"/>
-      <c r="W3" s="359"/>
-      <c r="X3" s="359"/>
-      <c r="Y3" s="359"/>
-      <c r="Z3" s="359"/>
-      <c r="AA3" s="359"/>
-      <c r="AB3" s="359"/>
-      <c r="AC3" s="359"/>
-      <c r="AD3" s="359"/>
-      <c r="AE3" s="359"/>
-      <c r="AF3" s="359"/>
-      <c r="AG3" s="359"/>
-      <c r="AH3" s="359"/>
-      <c r="AI3" s="359"/>
-      <c r="AJ3" s="359"/>
-      <c r="AK3" s="359"/>
-      <c r="AL3" s="359"/>
-      <c r="AM3" s="359"/>
-      <c r="AN3" s="359"/>
-      <c r="AO3" s="359"/>
-      <c r="AP3" s="359"/>
-      <c r="AQ3" s="359"/>
-      <c r="AR3" s="359"/>
-      <c r="AS3" s="359"/>
-      <c r="AT3" s="359"/>
-      <c r="AU3" s="359"/>
-      <c r="AV3" s="359"/>
-      <c r="AW3" s="359"/>
-      <c r="AX3" s="359"/>
-      <c r="AY3" s="359"/>
-      <c r="AZ3" s="359"/>
-      <c r="BA3" s="359"/>
-      <c r="BB3" s="359"/>
-      <c r="BC3" s="359"/>
-      <c r="BD3" s="359"/>
-      <c r="BE3" s="359"/>
-      <c r="BF3" s="359"/>
-      <c r="BG3" s="359"/>
-      <c r="BH3" s="359"/>
-      <c r="BI3" s="359"/>
-      <c r="BJ3" s="359"/>
-      <c r="BK3" s="359"/>
-      <c r="BL3" s="359"/>
-      <c r="BM3" s="359"/>
-      <c r="BN3" s="359"/>
-      <c r="BO3" s="359"/>
-      <c r="BP3" s="359"/>
-      <c r="BQ3" s="359"/>
-      <c r="BR3" s="359"/>
-      <c r="BS3" s="359"/>
-      <c r="BT3" s="359"/>
-      <c r="BU3" s="359"/>
+      <c r="B3" s="324"/>
+      <c r="C3" s="324"/>
+      <c r="D3" s="324"/>
+      <c r="E3" s="324"/>
+      <c r="F3" s="324"/>
+      <c r="G3" s="324"/>
+      <c r="H3" s="324"/>
+      <c r="I3" s="324"/>
+      <c r="J3" s="324"/>
+      <c r="K3" s="324"/>
+      <c r="L3" s="324"/>
+      <c r="M3" s="324"/>
+      <c r="N3" s="324"/>
+      <c r="O3" s="324"/>
+      <c r="P3" s="324"/>
+      <c r="Q3" s="324"/>
+      <c r="R3" s="324"/>
+      <c r="S3" s="324"/>
+      <c r="T3" s="324"/>
+      <c r="U3" s="324"/>
+      <c r="V3" s="324"/>
+      <c r="W3" s="324"/>
+      <c r="X3" s="324"/>
+      <c r="Y3" s="324"/>
+      <c r="Z3" s="324"/>
+      <c r="AA3" s="324"/>
+      <c r="AB3" s="324"/>
+      <c r="AC3" s="324"/>
+      <c r="AD3" s="324"/>
+      <c r="AE3" s="324"/>
+      <c r="AF3" s="324"/>
+      <c r="AG3" s="324"/>
+      <c r="AH3" s="324"/>
+      <c r="AI3" s="324"/>
+      <c r="AJ3" s="324"/>
+      <c r="AK3" s="324"/>
+      <c r="AL3" s="324"/>
+      <c r="AM3" s="324"/>
+      <c r="AN3" s="324"/>
+      <c r="AO3" s="324"/>
+      <c r="AP3" s="324"/>
+      <c r="AQ3" s="324"/>
+      <c r="AR3" s="324"/>
+      <c r="AS3" s="324"/>
+      <c r="AT3" s="324"/>
+      <c r="AU3" s="324"/>
+      <c r="AV3" s="324"/>
+      <c r="AW3" s="324"/>
+      <c r="AX3" s="324"/>
+      <c r="AY3" s="324"/>
+      <c r="AZ3" s="324"/>
+      <c r="BA3" s="324"/>
+      <c r="BB3" s="324"/>
+      <c r="BC3" s="324"/>
+      <c r="BD3" s="324"/>
+      <c r="BE3" s="324"/>
+      <c r="BF3" s="324"/>
+      <c r="BG3" s="324"/>
+      <c r="BH3" s="324"/>
+      <c r="BI3" s="324"/>
+      <c r="BJ3" s="324"/>
+      <c r="BK3" s="324"/>
+      <c r="BL3" s="324"/>
+      <c r="BM3" s="324"/>
+      <c r="BN3" s="324"/>
+      <c r="BO3" s="324"/>
+      <c r="BP3" s="324"/>
+      <c r="BQ3" s="324"/>
+      <c r="BR3" s="324"/>
+      <c r="BS3" s="324"/>
+      <c r="BT3" s="324"/>
+      <c r="BU3" s="324"/>
       <c r="BV3"/>
-      <c r="BW3" s="360" t="s">
+      <c r="BW3" s="325" t="s">
         <v>131</v>
       </c>
-      <c r="BX3" s="360"/>
-      <c r="BY3" s="360"/>
-      <c r="BZ3" s="360"/>
-      <c r="CA3" s="360"/>
-      <c r="CB3" s="359"/>
+      <c r="BX3" s="325"/>
+      <c r="BY3" s="325"/>
+      <c r="BZ3" s="325"/>
+      <c r="CA3" s="325"/>
+      <c r="CB3" s="324"/>
       <c r="CC3" s="110"/>
       <c r="CD3" s="110"/>
       <c r="CE3" s="236" t="s">
@@ -11041,366 +11042,366 @@
       <c r="BT4" s="237"/>
       <c r="BU4" s="237"/>
       <c r="BV4"/>
-      <c r="BW4" s="359"/>
-      <c r="BX4" s="359"/>
-      <c r="BY4" s="359"/>
-      <c r="BZ4" s="359"/>
-      <c r="CA4" s="359"/>
-      <c r="CB4" s="359"/>
+      <c r="BW4" s="324"/>
+      <c r="BX4" s="324"/>
+      <c r="BY4" s="324"/>
+      <c r="BZ4" s="324"/>
+      <c r="CA4" s="324"/>
+      <c r="CB4" s="324"/>
       <c r="CC4" s="110"/>
       <c r="CD4" s="110"/>
     </row>
     <row r="5" spans="1:87" s="2" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A5" s="361" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="362" t="s">
+      <c r="A5" s="326" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="329" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="331" t="s">
+      <c r="C5" s="330" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="363" t="s">
+      <c r="D5" s="331" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="363" t="s">
+      <c r="E5" s="331" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="331" t="s">
+      <c r="F5" s="330" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="358" t="s">
+      <c r="G5" s="332" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="364" t="s">
+      <c r="H5" s="333" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="364" t="s">
+      <c r="I5" s="333" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="358" t="s">
+      <c r="J5" s="332" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="365" t="s">
+      <c r="K5" s="334" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="352"/>
-      <c r="M5" s="352"/>
-      <c r="N5" s="352"/>
-      <c r="O5" s="352"/>
-      <c r="P5" s="352"/>
-      <c r="Q5" s="352"/>
-      <c r="R5" s="352"/>
-      <c r="S5" s="352"/>
-      <c r="T5" s="352"/>
-      <c r="U5" s="352"/>
-      <c r="V5" s="352"/>
-      <c r="W5" s="352"/>
-      <c r="X5" s="352"/>
-      <c r="Y5" s="358" t="s">
+      <c r="L5" s="335"/>
+      <c r="M5" s="335"/>
+      <c r="N5" s="335"/>
+      <c r="O5" s="335"/>
+      <c r="P5" s="335"/>
+      <c r="Q5" s="335"/>
+      <c r="R5" s="335"/>
+      <c r="S5" s="335"/>
+      <c r="T5" s="335"/>
+      <c r="U5" s="335"/>
+      <c r="V5" s="335"/>
+      <c r="W5" s="335"/>
+      <c r="X5" s="335"/>
+      <c r="Y5" s="332" t="s">
         <v>11</v>
       </c>
-      <c r="Z5" s="352"/>
-      <c r="AA5" s="352"/>
-      <c r="AB5" s="352"/>
-      <c r="AC5" s="352"/>
-      <c r="AD5" s="352"/>
-      <c r="AE5" s="352"/>
-      <c r="AF5" s="352"/>
-      <c r="AG5" s="352"/>
-      <c r="AH5" s="352"/>
-      <c r="AI5" s="352"/>
-      <c r="AJ5" s="352"/>
-      <c r="AK5" s="352"/>
-      <c r="AL5" s="352"/>
-      <c r="AM5" s="352"/>
-      <c r="AN5" s="352"/>
-      <c r="AO5" s="353"/>
-      <c r="AP5" s="358" t="s">
+      <c r="Z5" s="335"/>
+      <c r="AA5" s="335"/>
+      <c r="AB5" s="335"/>
+      <c r="AC5" s="335"/>
+      <c r="AD5" s="335"/>
+      <c r="AE5" s="335"/>
+      <c r="AF5" s="335"/>
+      <c r="AG5" s="335"/>
+      <c r="AH5" s="335"/>
+      <c r="AI5" s="335"/>
+      <c r="AJ5" s="335"/>
+      <c r="AK5" s="335"/>
+      <c r="AL5" s="335"/>
+      <c r="AM5" s="335"/>
+      <c r="AN5" s="335"/>
+      <c r="AO5" s="336"/>
+      <c r="AP5" s="332" t="s">
         <v>12</v>
       </c>
-      <c r="AQ5" s="358" t="s">
+      <c r="AQ5" s="332" t="s">
         <v>13</v>
       </c>
-      <c r="AR5" s="358" t="s">
+      <c r="AR5" s="332" t="s">
         <v>14</v>
       </c>
-      <c r="AS5" s="358" t="s">
+      <c r="AS5" s="332" t="s">
         <v>15</v>
       </c>
-      <c r="AT5" s="358" t="s">
+      <c r="AT5" s="332" t="s">
         <v>16</v>
       </c>
-      <c r="AU5" s="358" t="s">
+      <c r="AU5" s="332" t="s">
         <v>17</v>
       </c>
-      <c r="AV5" s="331" t="s">
+      <c r="AV5" s="330" t="s">
         <v>18</v>
       </c>
-      <c r="AW5" s="331" t="s">
+      <c r="AW5" s="330" t="s">
         <v>19</v>
       </c>
-      <c r="AX5" s="331" t="s">
+      <c r="AX5" s="330" t="s">
         <v>20</v>
       </c>
-      <c r="AY5" s="324" t="s">
+      <c r="AY5" s="337" t="s">
         <v>21</v>
       </c>
-      <c r="AZ5" s="352"/>
-      <c r="BA5" s="352"/>
-      <c r="BB5" s="352"/>
-      <c r="BC5" s="352"/>
-      <c r="BD5" s="352"/>
-      <c r="BE5" s="352"/>
-      <c r="BF5" s="352"/>
-      <c r="BG5" s="352"/>
-      <c r="BH5" s="352"/>
-      <c r="BI5" s="352"/>
-      <c r="BJ5" s="352"/>
-      <c r="BK5" s="352"/>
-      <c r="BL5" s="352"/>
-      <c r="BM5" s="352"/>
-      <c r="BN5" s="352"/>
-      <c r="BO5" s="352"/>
-      <c r="BP5" s="352"/>
-      <c r="BQ5" s="353"/>
-      <c r="BR5" s="354" t="s">
+      <c r="AZ5" s="335"/>
+      <c r="BA5" s="335"/>
+      <c r="BB5" s="335"/>
+      <c r="BC5" s="335"/>
+      <c r="BD5" s="335"/>
+      <c r="BE5" s="335"/>
+      <c r="BF5" s="335"/>
+      <c r="BG5" s="335"/>
+      <c r="BH5" s="335"/>
+      <c r="BI5" s="335"/>
+      <c r="BJ5" s="335"/>
+      <c r="BK5" s="335"/>
+      <c r="BL5" s="335"/>
+      <c r="BM5" s="335"/>
+      <c r="BN5" s="335"/>
+      <c r="BO5" s="335"/>
+      <c r="BP5" s="335"/>
+      <c r="BQ5" s="336"/>
+      <c r="BR5" s="338" t="s">
         <v>22</v>
       </c>
-      <c r="BS5" s="340"/>
-      <c r="BT5" s="324" t="s">
+      <c r="BS5" s="339"/>
+      <c r="BT5" s="337" t="s">
         <v>23</v>
       </c>
-      <c r="BU5" s="342" t="s">
+      <c r="BU5" s="344" t="s">
         <v>24</v>
       </c>
       <c r="BV5" s="226"/>
-      <c r="BW5" s="343" t="s">
+      <c r="BW5" s="347" t="s">
         <v>25</v>
       </c>
-      <c r="BX5" s="346" t="s">
+      <c r="BX5" s="350" t="s">
         <v>26</v>
       </c>
-      <c r="BY5" s="347"/>
-      <c r="BZ5" s="347"/>
-      <c r="CA5" s="340"/>
-      <c r="CB5" s="351" t="s">
+      <c r="BY5" s="351"/>
+      <c r="BZ5" s="351"/>
+      <c r="CA5" s="339"/>
+      <c r="CB5" s="355" t="s">
         <v>27</v>
       </c>
-      <c r="CC5" s="336" t="s">
+      <c r="CC5" s="357" t="s">
         <v>28</v>
       </c>
-      <c r="CD5" s="336" t="s">
+      <c r="CD5" s="357" t="s">
         <v>29</v>
       </c>
       <c r="CH5" s="16"/>
       <c r="CI5" s="17"/>
     </row>
     <row r="6" spans="1:87" s="2" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A6" s="332"/>
-      <c r="B6" s="332"/>
-      <c r="C6" s="332"/>
-      <c r="D6" s="332"/>
-      <c r="E6" s="332"/>
-      <c r="F6" s="332"/>
-      <c r="G6" s="332"/>
-      <c r="H6" s="332"/>
-      <c r="I6" s="332"/>
-      <c r="J6" s="332"/>
-      <c r="K6" s="338" t="s">
+      <c r="A6" s="327"/>
+      <c r="B6" s="327"/>
+      <c r="C6" s="327"/>
+      <c r="D6" s="327"/>
+      <c r="E6" s="327"/>
+      <c r="F6" s="327"/>
+      <c r="G6" s="327"/>
+      <c r="H6" s="327"/>
+      <c r="I6" s="327"/>
+      <c r="J6" s="327"/>
+      <c r="K6" s="358" t="s">
         <v>30</v>
       </c>
-      <c r="L6" s="338" t="s">
+      <c r="L6" s="358" t="s">
         <v>31</v>
       </c>
-      <c r="M6" s="338" t="s">
+      <c r="M6" s="358" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="338" t="s">
+      <c r="N6" s="358" t="s">
         <v>33</v>
       </c>
-      <c r="O6" s="338" t="s">
+      <c r="O6" s="358" t="s">
         <v>34</v>
       </c>
-      <c r="P6" s="338" t="s">
+      <c r="P6" s="358" t="s">
         <v>35</v>
       </c>
-      <c r="Q6" s="338" t="s">
+      <c r="Q6" s="358" t="s">
         <v>36</v>
       </c>
-      <c r="R6" s="338" t="s">
+      <c r="R6" s="358" t="s">
         <v>37</v>
       </c>
-      <c r="S6" s="338" t="s">
+      <c r="S6" s="358" t="s">
         <v>38</v>
       </c>
-      <c r="T6" s="338" t="s">
+      <c r="T6" s="358" t="s">
         <v>39</v>
       </c>
-      <c r="U6" s="338" t="s">
+      <c r="U6" s="358" t="s">
         <v>40</v>
       </c>
-      <c r="V6" s="339" t="s">
+      <c r="V6" s="359" t="s">
         <v>41</v>
       </c>
-      <c r="W6" s="340"/>
-      <c r="X6" s="338" t="s">
+      <c r="W6" s="339"/>
+      <c r="X6" s="358" t="s">
         <v>42</v>
       </c>
-      <c r="Y6" s="333" t="s">
+      <c r="Y6" s="361" t="s">
         <v>43</v>
       </c>
-      <c r="Z6" s="333" t="s">
+      <c r="Z6" s="361" t="s">
         <v>44</v>
       </c>
-      <c r="AA6" s="333" t="s">
+      <c r="AA6" s="361" t="s">
         <v>45</v>
       </c>
-      <c r="AB6" s="333" t="s">
+      <c r="AB6" s="361" t="s">
         <v>46</v>
       </c>
-      <c r="AC6" s="335" t="s">
+      <c r="AC6" s="362" t="s">
         <v>47</v>
       </c>
-      <c r="AD6" s="335" t="s">
+      <c r="AD6" s="362" t="s">
         <v>48</v>
       </c>
-      <c r="AE6" s="335" t="s">
+      <c r="AE6" s="362" t="s">
         <v>49</v>
       </c>
-      <c r="AF6" s="335" t="s">
+      <c r="AF6" s="362" t="s">
         <v>50</v>
       </c>
-      <c r="AG6" s="333" t="s">
+      <c r="AG6" s="361" t="s">
         <v>51</v>
       </c>
-      <c r="AH6" s="335" t="s">
+      <c r="AH6" s="362" t="s">
         <v>52</v>
       </c>
-      <c r="AI6" s="335" t="s">
+      <c r="AI6" s="362" t="s">
         <v>53</v>
       </c>
-      <c r="AJ6" s="333" t="s">
+      <c r="AJ6" s="361" t="s">
         <v>54</v>
       </c>
-      <c r="AK6" s="328" t="s">
+      <c r="AK6" s="363" t="s">
         <v>55</v>
       </c>
-      <c r="AL6" s="331" t="s">
+      <c r="AL6" s="330" t="s">
         <v>56</v>
       </c>
-      <c r="AM6" s="333" t="s">
+      <c r="AM6" s="361" t="s">
         <v>57</v>
       </c>
-      <c r="AN6" s="334" t="s">
+      <c r="AN6" s="364" t="s">
         <v>58</v>
       </c>
-      <c r="AO6" s="331" t="s">
+      <c r="AO6" s="330" t="s">
         <v>59</v>
       </c>
-      <c r="AP6" s="332"/>
-      <c r="AQ6" s="332"/>
-      <c r="AR6" s="332"/>
-      <c r="AS6" s="332"/>
-      <c r="AT6" s="332"/>
-      <c r="AU6" s="332"/>
-      <c r="AV6" s="332"/>
-      <c r="AW6" s="332"/>
-      <c r="AX6" s="332"/>
-      <c r="AY6" s="324" t="s">
+      <c r="AP6" s="327"/>
+      <c r="AQ6" s="327"/>
+      <c r="AR6" s="327"/>
+      <c r="AS6" s="327"/>
+      <c r="AT6" s="327"/>
+      <c r="AU6" s="327"/>
+      <c r="AV6" s="327"/>
+      <c r="AW6" s="327"/>
+      <c r="AX6" s="327"/>
+      <c r="AY6" s="337" t="s">
         <v>21</v>
       </c>
-      <c r="AZ6" s="352"/>
-      <c r="BA6" s="352"/>
-      <c r="BB6" s="352"/>
-      <c r="BC6" s="352"/>
-      <c r="BD6" s="352"/>
-      <c r="BE6" s="352"/>
-      <c r="BF6" s="352"/>
-      <c r="BG6" s="352"/>
-      <c r="BH6" s="352"/>
-      <c r="BI6" s="352"/>
-      <c r="BJ6" s="352"/>
-      <c r="BK6" s="352"/>
-      <c r="BL6" s="353"/>
-      <c r="BM6" s="324" t="s">
+      <c r="AZ6" s="335"/>
+      <c r="BA6" s="335"/>
+      <c r="BB6" s="335"/>
+      <c r="BC6" s="335"/>
+      <c r="BD6" s="335"/>
+      <c r="BE6" s="335"/>
+      <c r="BF6" s="335"/>
+      <c r="BG6" s="335"/>
+      <c r="BH6" s="335"/>
+      <c r="BI6" s="335"/>
+      <c r="BJ6" s="335"/>
+      <c r="BK6" s="335"/>
+      <c r="BL6" s="336"/>
+      <c r="BM6" s="337" t="s">
         <v>60</v>
       </c>
-      <c r="BN6" s="352"/>
-      <c r="BO6" s="352"/>
-      <c r="BP6" s="352"/>
-      <c r="BQ6" s="353"/>
-      <c r="BR6" s="355" t="s">
+      <c r="BN6" s="335"/>
+      <c r="BO6" s="335"/>
+      <c r="BP6" s="335"/>
+      <c r="BQ6" s="336"/>
+      <c r="BR6" s="340" t="s">
         <v>61</v>
       </c>
-      <c r="BS6" s="355" t="s">
+      <c r="BS6" s="340" t="s">
         <v>62</v>
       </c>
-      <c r="BT6" s="332"/>
-      <c r="BU6" s="329"/>
+      <c r="BT6" s="327"/>
+      <c r="BU6" s="345"/>
       <c r="BV6"/>
-      <c r="BW6" s="344"/>
-      <c r="BX6" s="329"/>
-      <c r="BY6" s="348"/>
-      <c r="BZ6" s="348"/>
-      <c r="CA6" s="344"/>
-      <c r="CB6" s="332"/>
-      <c r="CC6" s="332"/>
-      <c r="CD6" s="332"/>
+      <c r="BW6" s="348"/>
+      <c r="BX6" s="345"/>
+      <c r="BY6" s="352"/>
+      <c r="BZ6" s="352"/>
+      <c r="CA6" s="348"/>
+      <c r="CB6" s="327"/>
+      <c r="CC6" s="327"/>
+      <c r="CD6" s="327"/>
       <c r="CH6" s="16"/>
       <c r="CI6" s="17"/>
     </row>
     <row r="7" spans="1:87" s="18" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A7" s="332"/>
-      <c r="B7" s="332"/>
-      <c r="C7" s="332"/>
-      <c r="D7" s="332"/>
-      <c r="E7" s="332"/>
-      <c r="F7" s="332"/>
-      <c r="G7" s="332"/>
-      <c r="H7" s="332"/>
-      <c r="I7" s="332"/>
-      <c r="J7" s="332"/>
-      <c r="K7" s="332"/>
-      <c r="L7" s="332"/>
-      <c r="M7" s="332"/>
-      <c r="N7" s="332"/>
-      <c r="O7" s="332"/>
-      <c r="P7" s="332"/>
-      <c r="Q7" s="332"/>
-      <c r="R7" s="332"/>
-      <c r="S7" s="332"/>
-      <c r="T7" s="332"/>
-      <c r="U7" s="332"/>
-      <c r="V7" s="330"/>
-      <c r="W7" s="341"/>
-      <c r="X7" s="332"/>
-      <c r="Y7" s="332"/>
-      <c r="Z7" s="332"/>
-      <c r="AA7" s="332"/>
-      <c r="AB7" s="332"/>
-      <c r="AC7" s="332"/>
-      <c r="AD7" s="332"/>
-      <c r="AE7" s="332"/>
-      <c r="AF7" s="332"/>
-      <c r="AG7" s="332"/>
-      <c r="AH7" s="332"/>
-      <c r="AI7" s="332"/>
-      <c r="AJ7" s="332"/>
-      <c r="AK7" s="329"/>
-      <c r="AL7" s="332"/>
-      <c r="AM7" s="332"/>
-      <c r="AN7" s="332"/>
-      <c r="AO7" s="332"/>
-      <c r="AP7" s="332"/>
-      <c r="AQ7" s="332"/>
-      <c r="AR7" s="332"/>
-      <c r="AS7" s="332"/>
-      <c r="AT7" s="332"/>
-      <c r="AU7" s="332"/>
-      <c r="AV7" s="332"/>
-      <c r="AW7" s="332"/>
-      <c r="AX7" s="332"/>
+      <c r="A7" s="327"/>
+      <c r="B7" s="327"/>
+      <c r="C7" s="327"/>
+      <c r="D7" s="327"/>
+      <c r="E7" s="327"/>
+      <c r="F7" s="327"/>
+      <c r="G7" s="327"/>
+      <c r="H7" s="327"/>
+      <c r="I7" s="327"/>
+      <c r="J7" s="327"/>
+      <c r="K7" s="327"/>
+      <c r="L7" s="327"/>
+      <c r="M7" s="327"/>
+      <c r="N7" s="327"/>
+      <c r="O7" s="327"/>
+      <c r="P7" s="327"/>
+      <c r="Q7" s="327"/>
+      <c r="R7" s="327"/>
+      <c r="S7" s="327"/>
+      <c r="T7" s="327"/>
+      <c r="U7" s="327"/>
+      <c r="V7" s="346"/>
+      <c r="W7" s="360"/>
+      <c r="X7" s="327"/>
+      <c r="Y7" s="327"/>
+      <c r="Z7" s="327"/>
+      <c r="AA7" s="327"/>
+      <c r="AB7" s="327"/>
+      <c r="AC7" s="327"/>
+      <c r="AD7" s="327"/>
+      <c r="AE7" s="327"/>
+      <c r="AF7" s="327"/>
+      <c r="AG7" s="327"/>
+      <c r="AH7" s="327"/>
+      <c r="AI7" s="327"/>
+      <c r="AJ7" s="327"/>
+      <c r="AK7" s="345"/>
+      <c r="AL7" s="327"/>
+      <c r="AM7" s="327"/>
+      <c r="AN7" s="327"/>
+      <c r="AO7" s="327"/>
+      <c r="AP7" s="327"/>
+      <c r="AQ7" s="327"/>
+      <c r="AR7" s="327"/>
+      <c r="AS7" s="327"/>
+      <c r="AT7" s="327"/>
+      <c r="AU7" s="327"/>
+      <c r="AV7" s="327"/>
+      <c r="AW7" s="327"/>
+      <c r="AX7" s="327"/>
       <c r="AY7" s="88" t="s">
         <v>63</v>
       </c>
@@ -11410,125 +11411,125 @@
       <c r="BA7" s="88" t="s">
         <v>65</v>
       </c>
-      <c r="BB7" s="356" t="s">
+      <c r="BB7" s="341" t="s">
         <v>66</v>
       </c>
-      <c r="BC7" s="326" t="s">
+      <c r="BC7" s="342" t="s">
         <v>67</v>
       </c>
-      <c r="BD7" s="326" t="s">
+      <c r="BD7" s="342" t="s">
         <v>68</v>
       </c>
-      <c r="BE7" s="357" t="s">
+      <c r="BE7" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="BF7" s="326" t="s">
+      <c r="BF7" s="342" t="s">
         <v>70</v>
       </c>
-      <c r="BG7" s="326" t="s">
+      <c r="BG7" s="342" t="s">
         <v>71</v>
       </c>
-      <c r="BH7" s="326" t="s">
+      <c r="BH7" s="342" t="s">
         <v>72</v>
       </c>
-      <c r="BI7" s="326" t="s">
+      <c r="BI7" s="342" t="s">
         <v>73</v>
       </c>
-      <c r="BJ7" s="326" t="s">
+      <c r="BJ7" s="342" t="s">
         <v>74</v>
       </c>
-      <c r="BK7" s="326" t="s">
+      <c r="BK7" s="342" t="s">
         <v>75</v>
       </c>
-      <c r="BL7" s="327" t="s">
+      <c r="BL7" s="365" t="s">
         <v>76</v>
       </c>
-      <c r="BM7" s="326" t="s">
+      <c r="BM7" s="342" t="s">
         <v>77</v>
       </c>
-      <c r="BN7" s="324" t="s">
+      <c r="BN7" s="337" t="s">
         <v>78</v>
       </c>
-      <c r="BO7" s="326" t="s">
+      <c r="BO7" s="342" t="s">
         <v>79</v>
       </c>
-      <c r="BP7" s="324" t="s">
+      <c r="BP7" s="337" t="s">
         <v>80</v>
       </c>
-      <c r="BQ7" s="324" t="s">
+      <c r="BQ7" s="337" t="s">
         <v>81</v>
       </c>
-      <c r="BR7" s="332"/>
-      <c r="BS7" s="332"/>
-      <c r="BT7" s="332"/>
-      <c r="BU7" s="329"/>
+      <c r="BR7" s="327"/>
+      <c r="BS7" s="327"/>
+      <c r="BT7" s="327"/>
+      <c r="BU7" s="345"/>
       <c r="BV7"/>
-      <c r="BW7" s="344"/>
-      <c r="BX7" s="349"/>
-      <c r="BY7" s="350"/>
-      <c r="BZ7" s="350"/>
-      <c r="CA7" s="345"/>
-      <c r="CB7" s="332"/>
-      <c r="CC7" s="332"/>
-      <c r="CD7" s="332"/>
+      <c r="BW7" s="348"/>
+      <c r="BX7" s="353"/>
+      <c r="BY7" s="354"/>
+      <c r="BZ7" s="354"/>
+      <c r="CA7" s="349"/>
+      <c r="CB7" s="327"/>
+      <c r="CC7" s="327"/>
+      <c r="CD7" s="327"/>
       <c r="CH7" s="16"/>
       <c r="CI7" s="17"/>
     </row>
     <row r="8" spans="1:87" s="18" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A8" s="325"/>
-      <c r="B8" s="325"/>
-      <c r="C8" s="325"/>
-      <c r="D8" s="325"/>
-      <c r="E8" s="325"/>
-      <c r="F8" s="325"/>
-      <c r="G8" s="325"/>
-      <c r="H8" s="325"/>
-      <c r="I8" s="325"/>
-      <c r="J8" s="325"/>
-      <c r="K8" s="325"/>
-      <c r="L8" s="325"/>
-      <c r="M8" s="325"/>
-      <c r="N8" s="325"/>
-      <c r="O8" s="325"/>
-      <c r="P8" s="325"/>
-      <c r="Q8" s="325"/>
-      <c r="R8" s="325"/>
-      <c r="S8" s="325"/>
-      <c r="T8" s="325"/>
-      <c r="U8" s="325"/>
+      <c r="A8" s="328"/>
+      <c r="B8" s="328"/>
+      <c r="C8" s="328"/>
+      <c r="D8" s="328"/>
+      <c r="E8" s="328"/>
+      <c r="F8" s="328"/>
+      <c r="G8" s="328"/>
+      <c r="H8" s="328"/>
+      <c r="I8" s="328"/>
+      <c r="J8" s="328"/>
+      <c r="K8" s="328"/>
+      <c r="L8" s="328"/>
+      <c r="M8" s="328"/>
+      <c r="N8" s="328"/>
+      <c r="O8" s="328"/>
+      <c r="P8" s="328"/>
+      <c r="Q8" s="328"/>
+      <c r="R8" s="328"/>
+      <c r="S8" s="328"/>
+      <c r="T8" s="328"/>
+      <c r="U8" s="328"/>
       <c r="V8" s="19" t="s">
         <v>82</v>
       </c>
       <c r="W8" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="X8" s="325"/>
-      <c r="Y8" s="325"/>
-      <c r="Z8" s="325"/>
-      <c r="AA8" s="325"/>
-      <c r="AB8" s="325"/>
-      <c r="AC8" s="325"/>
-      <c r="AD8" s="325"/>
-      <c r="AE8" s="325"/>
-      <c r="AF8" s="325"/>
-      <c r="AG8" s="325"/>
-      <c r="AH8" s="325"/>
-      <c r="AI8" s="325"/>
-      <c r="AJ8" s="325"/>
-      <c r="AK8" s="330"/>
-      <c r="AL8" s="325"/>
-      <c r="AM8" s="325"/>
-      <c r="AN8" s="325"/>
-      <c r="AO8" s="325"/>
-      <c r="AP8" s="325"/>
-      <c r="AQ8" s="325"/>
-      <c r="AR8" s="325"/>
-      <c r="AS8" s="325"/>
-      <c r="AT8" s="325"/>
-      <c r="AU8" s="325"/>
-      <c r="AV8" s="325"/>
-      <c r="AW8" s="325"/>
-      <c r="AX8" s="325"/>
+      <c r="X8" s="328"/>
+      <c r="Y8" s="328"/>
+      <c r="Z8" s="328"/>
+      <c r="AA8" s="328"/>
+      <c r="AB8" s="328"/>
+      <c r="AC8" s="328"/>
+      <c r="AD8" s="328"/>
+      <c r="AE8" s="328"/>
+      <c r="AF8" s="328"/>
+      <c r="AG8" s="328"/>
+      <c r="AH8" s="328"/>
+      <c r="AI8" s="328"/>
+      <c r="AJ8" s="328"/>
+      <c r="AK8" s="346"/>
+      <c r="AL8" s="328"/>
+      <c r="AM8" s="328"/>
+      <c r="AN8" s="328"/>
+      <c r="AO8" s="328"/>
+      <c r="AP8" s="328"/>
+      <c r="AQ8" s="328"/>
+      <c r="AR8" s="328"/>
+      <c r="AS8" s="328"/>
+      <c r="AT8" s="328"/>
+      <c r="AU8" s="328"/>
+      <c r="AV8" s="328"/>
+      <c r="AW8" s="328"/>
+      <c r="AX8" s="328"/>
       <c r="AY8" s="227" t="s">
         <v>84</v>
       </c>
@@ -11538,28 +11539,28 @@
       <c r="BA8" s="227" t="s">
         <v>86</v>
       </c>
-      <c r="BB8" s="325"/>
-      <c r="BC8" s="325"/>
-      <c r="BD8" s="325"/>
-      <c r="BE8" s="325"/>
-      <c r="BF8" s="325"/>
-      <c r="BG8" s="325"/>
-      <c r="BH8" s="325"/>
-      <c r="BI8" s="325"/>
-      <c r="BJ8" s="325"/>
-      <c r="BK8" s="325"/>
-      <c r="BL8" s="325"/>
-      <c r="BM8" s="325"/>
-      <c r="BN8" s="325"/>
-      <c r="BO8" s="325"/>
-      <c r="BP8" s="325"/>
-      <c r="BQ8" s="325"/>
-      <c r="BR8" s="325"/>
-      <c r="BS8" s="325"/>
-      <c r="BT8" s="325"/>
-      <c r="BU8" s="330"/>
+      <c r="BB8" s="328"/>
+      <c r="BC8" s="328"/>
+      <c r="BD8" s="328"/>
+      <c r="BE8" s="328"/>
+      <c r="BF8" s="328"/>
+      <c r="BG8" s="328"/>
+      <c r="BH8" s="328"/>
+      <c r="BI8" s="328"/>
+      <c r="BJ8" s="328"/>
+      <c r="BK8" s="328"/>
+      <c r="BL8" s="328"/>
+      <c r="BM8" s="328"/>
+      <c r="BN8" s="328"/>
+      <c r="BO8" s="328"/>
+      <c r="BP8" s="328"/>
+      <c r="BQ8" s="328"/>
+      <c r="BR8" s="328"/>
+      <c r="BS8" s="328"/>
+      <c r="BT8" s="328"/>
+      <c r="BU8" s="346"/>
       <c r="BV8"/>
-      <c r="BW8" s="345"/>
+      <c r="BW8" s="349"/>
       <c r="BX8" s="61" t="s">
         <v>87</v>
       </c>
@@ -11572,9 +11573,9 @@
       <c r="CA8" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="CB8" s="337"/>
-      <c r="CC8" s="337"/>
-      <c r="CD8" s="337"/>
+      <c r="CB8" s="356"/>
+      <c r="CC8" s="356"/>
+      <c r="CD8" s="356"/>
       <c r="CE8" s="2"/>
       <c r="CF8" s="20"/>
       <c r="CH8" s="16"/>
@@ -14235,6 +14236,72 @@
   </sheetData>
   <autoFilter ref="A5:CI10" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="82">
+    <mergeCell ref="BN7:BN8"/>
+    <mergeCell ref="BO7:BO8"/>
+    <mergeCell ref="BP7:BP8"/>
+    <mergeCell ref="BQ7:BQ8"/>
+    <mergeCell ref="BI7:BI8"/>
+    <mergeCell ref="BJ7:BJ8"/>
+    <mergeCell ref="BK7:BK8"/>
+    <mergeCell ref="BL7:BL8"/>
+    <mergeCell ref="BM7:BM8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="CD5:CD8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="BU5:BU8"/>
+    <mergeCell ref="BW5:BW8"/>
+    <mergeCell ref="BX5:CA7"/>
+    <mergeCell ref="CB5:CB8"/>
+    <mergeCell ref="CC5:CC8"/>
+    <mergeCell ref="AW5:AW8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="AY5:BQ5"/>
+    <mergeCell ref="BR5:BS5"/>
+    <mergeCell ref="BT5:BT8"/>
+    <mergeCell ref="AY6:BL6"/>
+    <mergeCell ref="BM6:BQ6"/>
+    <mergeCell ref="BR6:BR8"/>
+    <mergeCell ref="BS6:BS8"/>
+    <mergeCell ref="BB7:BB8"/>
+    <mergeCell ref="BC7:BC8"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="BF7:BF8"/>
+    <mergeCell ref="BG7:BG8"/>
+    <mergeCell ref="BH7:BH8"/>
+    <mergeCell ref="AR5:AR8"/>
+    <mergeCell ref="AS5:AS8"/>
+    <mergeCell ref="AT5:AT8"/>
+    <mergeCell ref="AU5:AU8"/>
+    <mergeCell ref="AV5:AV8"/>
     <mergeCell ref="A3:BU3"/>
     <mergeCell ref="BW3:CB4"/>
     <mergeCell ref="A5:A8"/>
@@ -14251,72 +14318,6 @@
     <mergeCell ref="Y5:AO5"/>
     <mergeCell ref="AP5:AP8"/>
     <mergeCell ref="AQ5:AQ8"/>
-    <mergeCell ref="AR5:AR8"/>
-    <mergeCell ref="AS5:AS8"/>
-    <mergeCell ref="AT5:AT8"/>
-    <mergeCell ref="AU5:AU8"/>
-    <mergeCell ref="AV5:AV8"/>
-    <mergeCell ref="AW5:AW8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="AY5:BQ5"/>
-    <mergeCell ref="BR5:BS5"/>
-    <mergeCell ref="BT5:BT8"/>
-    <mergeCell ref="AY6:BL6"/>
-    <mergeCell ref="BM6:BQ6"/>
-    <mergeCell ref="BR6:BR8"/>
-    <mergeCell ref="BS6:BS8"/>
-    <mergeCell ref="BB7:BB8"/>
-    <mergeCell ref="BC7:BC8"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="BF7:BF8"/>
-    <mergeCell ref="BG7:BG8"/>
-    <mergeCell ref="BH7:BH8"/>
-    <mergeCell ref="BU5:BU8"/>
-    <mergeCell ref="BW5:BW8"/>
-    <mergeCell ref="BX5:CA7"/>
-    <mergeCell ref="CB5:CB8"/>
-    <mergeCell ref="CC5:CC8"/>
-    <mergeCell ref="CD5:CD8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="P6:P8"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="BN7:BN8"/>
-    <mergeCell ref="BO7:BO8"/>
-    <mergeCell ref="BP7:BP8"/>
-    <mergeCell ref="BQ7:BQ8"/>
-    <mergeCell ref="BI7:BI8"/>
-    <mergeCell ref="BJ7:BJ8"/>
-    <mergeCell ref="BK7:BK8"/>
-    <mergeCell ref="BL7:BL8"/>
-    <mergeCell ref="BM7:BM8"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B8">
     <cfRule type="duplicateValues" dxfId="27" priority="1"/>
@@ -14324,15 +14325,15 @@
     <cfRule type="duplicateValues" dxfId="25" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:B16 B1:B4 B20:B1048576 B9:BU9">
-    <cfRule type="duplicateValues" dxfId="24" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:B16 B1:B4 D10:F10 J10:BK10 BM10:BU10 B20:B1048576 BW9:CD10 B9:BU9">
     <cfRule type="duplicateValues" dxfId="22" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:C19">
-    <cfRule type="duplicateValues" dxfId="21" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="4"/>
     <cfRule type="duplicateValues" dxfId="19" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL10">
@@ -14544,91 +14545,91 @@
       <c r="CD2" s="223"/>
     </row>
     <row r="3" spans="1:87" s="5" customFormat="1" ht="30" outlineLevel="1">
-      <c r="A3" s="370" t="str">
+      <c r="A3" s="366" t="str">
         <f ca="1">"BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …."&amp;" NĂM "&amp;YEAR(NOW())</f>
         <v>BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …. NĂM 2026</v>
       </c>
-      <c r="B3" s="370"/>
-      <c r="C3" s="370"/>
-      <c r="D3" s="370"/>
-      <c r="E3" s="370"/>
-      <c r="F3" s="370"/>
-      <c r="G3" s="370"/>
-      <c r="H3" s="370"/>
-      <c r="I3" s="370"/>
-      <c r="J3" s="370"/>
-      <c r="K3" s="370"/>
-      <c r="L3" s="370"/>
-      <c r="M3" s="370"/>
-      <c r="N3" s="370"/>
-      <c r="O3" s="370"/>
-      <c r="P3" s="370"/>
-      <c r="Q3" s="370"/>
-      <c r="R3" s="370"/>
-      <c r="S3" s="370"/>
-      <c r="T3" s="370"/>
-      <c r="U3" s="370"/>
-      <c r="V3" s="370"/>
-      <c r="W3" s="370"/>
-      <c r="X3" s="370"/>
-      <c r="Y3" s="370"/>
-      <c r="Z3" s="370"/>
-      <c r="AA3" s="370"/>
-      <c r="AB3" s="370"/>
-      <c r="AC3" s="370"/>
-      <c r="AD3" s="370"/>
-      <c r="AE3" s="370"/>
-      <c r="AF3" s="370"/>
-      <c r="AG3" s="370"/>
-      <c r="AH3" s="370"/>
-      <c r="AI3" s="370"/>
-      <c r="AJ3" s="370"/>
-      <c r="AK3" s="370"/>
-      <c r="AL3" s="370"/>
-      <c r="AM3" s="370"/>
-      <c r="AN3" s="370"/>
-      <c r="AO3" s="370"/>
-      <c r="AP3" s="370"/>
-      <c r="AQ3" s="370"/>
-      <c r="AR3" s="370"/>
-      <c r="AS3" s="370"/>
-      <c r="AT3" s="370"/>
-      <c r="AU3" s="370"/>
-      <c r="AV3" s="370"/>
-      <c r="AW3" s="370"/>
-      <c r="AX3" s="370"/>
-      <c r="AY3" s="370"/>
-      <c r="AZ3" s="370"/>
-      <c r="BA3" s="370"/>
-      <c r="BB3" s="370"/>
-      <c r="BC3" s="370"/>
-      <c r="BD3" s="370"/>
-      <c r="BE3" s="370"/>
-      <c r="BF3" s="370"/>
-      <c r="BG3" s="370"/>
-      <c r="BH3" s="370"/>
-      <c r="BI3" s="370"/>
-      <c r="BJ3" s="370"/>
-      <c r="BK3" s="370"/>
-      <c r="BL3" s="370"/>
-      <c r="BM3" s="370"/>
-      <c r="BN3" s="370"/>
-      <c r="BO3" s="370"/>
-      <c r="BP3" s="370"/>
-      <c r="BQ3" s="370"/>
-      <c r="BR3" s="370"/>
-      <c r="BS3" s="370"/>
-      <c r="BT3" s="370"/>
-      <c r="BU3" s="370"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
+      <c r="L3" s="366"/>
+      <c r="M3" s="366"/>
+      <c r="N3" s="366"/>
+      <c r="O3" s="366"/>
+      <c r="P3" s="366"/>
+      <c r="Q3" s="366"/>
+      <c r="R3" s="366"/>
+      <c r="S3" s="366"/>
+      <c r="T3" s="366"/>
+      <c r="U3" s="366"/>
+      <c r="V3" s="366"/>
+      <c r="W3" s="366"/>
+      <c r="X3" s="366"/>
+      <c r="Y3" s="366"/>
+      <c r="Z3" s="366"/>
+      <c r="AA3" s="366"/>
+      <c r="AB3" s="366"/>
+      <c r="AC3" s="366"/>
+      <c r="AD3" s="366"/>
+      <c r="AE3" s="366"/>
+      <c r="AF3" s="366"/>
+      <c r="AG3" s="366"/>
+      <c r="AH3" s="366"/>
+      <c r="AI3" s="366"/>
+      <c r="AJ3" s="366"/>
+      <c r="AK3" s="366"/>
+      <c r="AL3" s="366"/>
+      <c r="AM3" s="366"/>
+      <c r="AN3" s="366"/>
+      <c r="AO3" s="366"/>
+      <c r="AP3" s="366"/>
+      <c r="AQ3" s="366"/>
+      <c r="AR3" s="366"/>
+      <c r="AS3" s="366"/>
+      <c r="AT3" s="366"/>
+      <c r="AU3" s="366"/>
+      <c r="AV3" s="366"/>
+      <c r="AW3" s="366"/>
+      <c r="AX3" s="366"/>
+      <c r="AY3" s="366"/>
+      <c r="AZ3" s="366"/>
+      <c r="BA3" s="366"/>
+      <c r="BB3" s="366"/>
+      <c r="BC3" s="366"/>
+      <c r="BD3" s="366"/>
+      <c r="BE3" s="366"/>
+      <c r="BF3" s="366"/>
+      <c r="BG3" s="366"/>
+      <c r="BH3" s="366"/>
+      <c r="BI3" s="366"/>
+      <c r="BJ3" s="366"/>
+      <c r="BK3" s="366"/>
+      <c r="BL3" s="366"/>
+      <c r="BM3" s="366"/>
+      <c r="BN3" s="366"/>
+      <c r="BO3" s="366"/>
+      <c r="BP3" s="366"/>
+      <c r="BQ3" s="366"/>
+      <c r="BR3" s="366"/>
+      <c r="BS3" s="366"/>
+      <c r="BT3" s="366"/>
+      <c r="BU3" s="366"/>
       <c r="BV3" s="225"/>
-      <c r="BW3" s="371" t="s">
+      <c r="BW3" s="367" t="s">
         <v>131</v>
       </c>
-      <c r="BX3" s="371"/>
-      <c r="BY3" s="371"/>
-      <c r="BZ3" s="371"/>
-      <c r="CA3" s="371"/>
-      <c r="CB3" s="372"/>
+      <c r="BX3" s="367"/>
+      <c r="BY3" s="367"/>
+      <c r="BZ3" s="367"/>
+      <c r="CA3" s="367"/>
+      <c r="CB3" s="368"/>
       <c r="CC3" s="60"/>
       <c r="CD3" s="60"/>
       <c r="CE3" s="5" t="s">
@@ -14712,12 +14713,12 @@
       <c r="BT4" s="4"/>
       <c r="BU4" s="4"/>
       <c r="BV4" s="96"/>
-      <c r="BW4" s="372"/>
-      <c r="BX4" s="372"/>
-      <c r="BY4" s="372"/>
-      <c r="BZ4" s="372"/>
-      <c r="CA4" s="372"/>
-      <c r="CB4" s="372"/>
+      <c r="BW4" s="368"/>
+      <c r="BX4" s="368"/>
+      <c r="BY4" s="368"/>
+      <c r="BZ4" s="368"/>
+      <c r="CA4" s="368"/>
+      <c r="CB4" s="368"/>
       <c r="CC4" s="60"/>
       <c r="CD4" s="60"/>
     </row>
@@ -14795,12 +14796,12 @@
       <c r="BT5" s="4"/>
       <c r="BU5" s="4"/>
       <c r="BV5" s="96"/>
-      <c r="BW5" s="372"/>
-      <c r="BX5" s="372"/>
-      <c r="BY5" s="372"/>
-      <c r="BZ5" s="372"/>
-      <c r="CA5" s="372"/>
-      <c r="CB5" s="372"/>
+      <c r="BW5" s="368"/>
+      <c r="BX5" s="368"/>
+      <c r="BY5" s="368"/>
+      <c r="BZ5" s="368"/>
+      <c r="CA5" s="368"/>
+      <c r="CB5" s="368"/>
       <c r="CC5" s="60"/>
       <c r="CD5" s="60"/>
     </row>
@@ -14878,12 +14879,12 @@
       <c r="BT6" s="7"/>
       <c r="BU6" s="7"/>
       <c r="BV6" s="97"/>
-      <c r="BW6" s="371"/>
-      <c r="BX6" s="371"/>
-      <c r="BY6" s="371"/>
-      <c r="BZ6" s="371"/>
-      <c r="CA6" s="371"/>
-      <c r="CB6" s="372"/>
+      <c r="BW6" s="367"/>
+      <c r="BX6" s="367"/>
+      <c r="BY6" s="367"/>
+      <c r="BZ6" s="367"/>
+      <c r="CA6" s="367"/>
+      <c r="CB6" s="368"/>
       <c r="CC6" s="60"/>
       <c r="CD6" s="60"/>
     </row>
@@ -14971,358 +14972,358 @@
       <c r="CD7" s="14"/>
     </row>
     <row r="8" spans="1:87" s="2" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="361" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="362" t="s">
+      <c r="A8" s="326" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="329" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="331" t="s">
+      <c r="C8" s="330" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="363" t="s">
+      <c r="D8" s="331" t="s">
         <v>117</v>
       </c>
-      <c r="E8" s="363" t="s">
+      <c r="E8" s="331" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="373" t="s">
+      <c r="F8" s="369" t="s">
         <v>118</v>
       </c>
-      <c r="G8" s="358" t="s">
+      <c r="G8" s="332" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="364" t="s">
+      <c r="H8" s="333" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="364" t="s">
+      <c r="I8" s="333" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="358" t="s">
+      <c r="J8" s="332" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="365" t="s">
+      <c r="K8" s="334" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="352"/>
-      <c r="M8" s="352"/>
-      <c r="N8" s="352"/>
-      <c r="O8" s="352"/>
-      <c r="P8" s="352"/>
-      <c r="Q8" s="352"/>
-      <c r="R8" s="352"/>
-      <c r="S8" s="352"/>
-      <c r="T8" s="352"/>
-      <c r="U8" s="352"/>
-      <c r="V8" s="352"/>
-      <c r="W8" s="352"/>
-      <c r="X8" s="352"/>
-      <c r="Y8" s="358" t="s">
+      <c r="L8" s="335"/>
+      <c r="M8" s="335"/>
+      <c r="N8" s="335"/>
+      <c r="O8" s="335"/>
+      <c r="P8" s="335"/>
+      <c r="Q8" s="335"/>
+      <c r="R8" s="335"/>
+      <c r="S8" s="335"/>
+      <c r="T8" s="335"/>
+      <c r="U8" s="335"/>
+      <c r="V8" s="335"/>
+      <c r="W8" s="335"/>
+      <c r="X8" s="335"/>
+      <c r="Y8" s="332" t="s">
         <v>11</v>
       </c>
-      <c r="Z8" s="352"/>
-      <c r="AA8" s="352"/>
-      <c r="AB8" s="352"/>
-      <c r="AC8" s="352"/>
-      <c r="AD8" s="352"/>
-      <c r="AE8" s="352"/>
-      <c r="AF8" s="352"/>
-      <c r="AG8" s="352"/>
-      <c r="AH8" s="352"/>
-      <c r="AI8" s="352"/>
-      <c r="AJ8" s="352"/>
-      <c r="AK8" s="352"/>
-      <c r="AL8" s="352"/>
-      <c r="AM8" s="352"/>
-      <c r="AN8" s="352"/>
-      <c r="AO8" s="353"/>
-      <c r="AP8" s="358" t="s">
+      <c r="Z8" s="335"/>
+      <c r="AA8" s="335"/>
+      <c r="AB8" s="335"/>
+      <c r="AC8" s="335"/>
+      <c r="AD8" s="335"/>
+      <c r="AE8" s="335"/>
+      <c r="AF8" s="335"/>
+      <c r="AG8" s="335"/>
+      <c r="AH8" s="335"/>
+      <c r="AI8" s="335"/>
+      <c r="AJ8" s="335"/>
+      <c r="AK8" s="335"/>
+      <c r="AL8" s="335"/>
+      <c r="AM8" s="335"/>
+      <c r="AN8" s="335"/>
+      <c r="AO8" s="336"/>
+      <c r="AP8" s="332" t="s">
         <v>12</v>
       </c>
-      <c r="AQ8" s="358" t="s">
+      <c r="AQ8" s="332" t="s">
         <v>13</v>
       </c>
-      <c r="AR8" s="358" t="s">
+      <c r="AR8" s="332" t="s">
         <v>14</v>
       </c>
-      <c r="AS8" s="358" t="s">
+      <c r="AS8" s="332" t="s">
         <v>15</v>
       </c>
-      <c r="AT8" s="358" t="s">
+      <c r="AT8" s="332" t="s">
         <v>16</v>
       </c>
-      <c r="AU8" s="358" t="s">
+      <c r="AU8" s="332" t="s">
         <v>17</v>
       </c>
-      <c r="AV8" s="331" t="s">
+      <c r="AV8" s="330" t="s">
         <v>18</v>
       </c>
-      <c r="AW8" s="331" t="s">
+      <c r="AW8" s="330" t="s">
         <v>19</v>
       </c>
-      <c r="AX8" s="331" t="s">
+      <c r="AX8" s="330" t="s">
         <v>20</v>
       </c>
-      <c r="AY8" s="324" t="s">
+      <c r="AY8" s="337" t="s">
         <v>21</v>
       </c>
-      <c r="AZ8" s="352"/>
-      <c r="BA8" s="352"/>
-      <c r="BB8" s="352"/>
-      <c r="BC8" s="352"/>
-      <c r="BD8" s="352"/>
-      <c r="BE8" s="352"/>
-      <c r="BF8" s="352"/>
-      <c r="BG8" s="352"/>
-      <c r="BH8" s="352"/>
-      <c r="BI8" s="352"/>
-      <c r="BJ8" s="352"/>
-      <c r="BK8" s="352"/>
-      <c r="BL8" s="352"/>
-      <c r="BM8" s="352"/>
-      <c r="BN8" s="352"/>
-      <c r="BO8" s="352"/>
-      <c r="BP8" s="353"/>
-      <c r="BQ8" s="354" t="s">
+      <c r="AZ8" s="335"/>
+      <c r="BA8" s="335"/>
+      <c r="BB8" s="335"/>
+      <c r="BC8" s="335"/>
+      <c r="BD8" s="335"/>
+      <c r="BE8" s="335"/>
+      <c r="BF8" s="335"/>
+      <c r="BG8" s="335"/>
+      <c r="BH8" s="335"/>
+      <c r="BI8" s="335"/>
+      <c r="BJ8" s="335"/>
+      <c r="BK8" s="335"/>
+      <c r="BL8" s="335"/>
+      <c r="BM8" s="335"/>
+      <c r="BN8" s="335"/>
+      <c r="BO8" s="335"/>
+      <c r="BP8" s="336"/>
+      <c r="BQ8" s="338" t="s">
         <v>22</v>
       </c>
-      <c r="BR8" s="340"/>
-      <c r="BS8" s="324" t="s">
+      <c r="BR8" s="339"/>
+      <c r="BS8" s="337" t="s">
         <v>119</v>
       </c>
-      <c r="BT8" s="324" t="s">
+      <c r="BT8" s="337" t="s">
         <v>23</v>
       </c>
-      <c r="BU8" s="342" t="s">
+      <c r="BU8" s="344" t="s">
         <v>24</v>
       </c>
       <c r="BV8" s="99"/>
-      <c r="BW8" s="343" t="s">
+      <c r="BW8" s="347" t="s">
         <v>25</v>
       </c>
-      <c r="BX8" s="346" t="s">
+      <c r="BX8" s="350" t="s">
         <v>26</v>
       </c>
-      <c r="BY8" s="347"/>
-      <c r="BZ8" s="347"/>
-      <c r="CA8" s="340"/>
-      <c r="CB8" s="351" t="s">
+      <c r="BY8" s="351"/>
+      <c r="BZ8" s="351"/>
+      <c r="CA8" s="339"/>
+      <c r="CB8" s="355" t="s">
         <v>27</v>
       </c>
-      <c r="CC8" s="336" t="s">
+      <c r="CC8" s="357" t="s">
         <v>28</v>
       </c>
-      <c r="CD8" s="336" t="s">
+      <c r="CD8" s="357" t="s">
         <v>29</v>
       </c>
       <c r="CH8" s="16"/>
       <c r="CI8" s="17"/>
     </row>
     <row r="9" spans="1:87" s="2" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="332"/>
-      <c r="B9" s="332"/>
-      <c r="C9" s="332"/>
-      <c r="D9" s="332"/>
-      <c r="E9" s="332"/>
-      <c r="F9" s="332"/>
-      <c r="G9" s="332"/>
-      <c r="H9" s="332"/>
-      <c r="I9" s="332"/>
-      <c r="J9" s="332"/>
-      <c r="K9" s="338" t="s">
+      <c r="A9" s="327"/>
+      <c r="B9" s="327"/>
+      <c r="C9" s="327"/>
+      <c r="D9" s="327"/>
+      <c r="E9" s="327"/>
+      <c r="F9" s="327"/>
+      <c r="G9" s="327"/>
+      <c r="H9" s="327"/>
+      <c r="I9" s="327"/>
+      <c r="J9" s="327"/>
+      <c r="K9" s="358" t="s">
         <v>30</v>
       </c>
-      <c r="L9" s="338" t="s">
+      <c r="L9" s="358" t="s">
         <v>31</v>
       </c>
-      <c r="M9" s="338" t="s">
+      <c r="M9" s="358" t="s">
         <v>32</v>
       </c>
-      <c r="N9" s="338" t="s">
+      <c r="N9" s="358" t="s">
         <v>33</v>
       </c>
-      <c r="O9" s="338" t="s">
+      <c r="O9" s="358" t="s">
         <v>34</v>
       </c>
-      <c r="P9" s="338" t="s">
+      <c r="P9" s="358" t="s">
         <v>35</v>
       </c>
-      <c r="Q9" s="338" t="s">
+      <c r="Q9" s="358" t="s">
         <v>36</v>
       </c>
-      <c r="R9" s="338" t="s">
+      <c r="R9" s="358" t="s">
         <v>37</v>
       </c>
-      <c r="S9" s="338" t="s">
+      <c r="S9" s="358" t="s">
         <v>38</v>
       </c>
-      <c r="T9" s="338" t="s">
+      <c r="T9" s="358" t="s">
         <v>39</v>
       </c>
-      <c r="U9" s="338" t="s">
+      <c r="U9" s="358" t="s">
         <v>40</v>
       </c>
-      <c r="V9" s="339" t="s">
+      <c r="V9" s="359" t="s">
         <v>41</v>
       </c>
-      <c r="W9" s="340"/>
-      <c r="X9" s="338" t="s">
+      <c r="W9" s="339"/>
+      <c r="X9" s="358" t="s">
         <v>42</v>
       </c>
-      <c r="Y9" s="333" t="s">
+      <c r="Y9" s="361" t="s">
         <v>43</v>
       </c>
-      <c r="Z9" s="333" t="s">
+      <c r="Z9" s="361" t="s">
         <v>44</v>
       </c>
-      <c r="AA9" s="333" t="s">
+      <c r="AA9" s="361" t="s">
         <v>45</v>
       </c>
-      <c r="AB9" s="333" t="s">
+      <c r="AB9" s="361" t="s">
         <v>46</v>
       </c>
-      <c r="AC9" s="335" t="s">
+      <c r="AC9" s="362" t="s">
         <v>47</v>
       </c>
-      <c r="AD9" s="335" t="s">
+      <c r="AD9" s="362" t="s">
         <v>120</v>
       </c>
-      <c r="AE9" s="335" t="s">
+      <c r="AE9" s="362" t="s">
         <v>49</v>
       </c>
-      <c r="AF9" s="335" t="s">
+      <c r="AF9" s="362" t="s">
         <v>50</v>
       </c>
-      <c r="AG9" s="333" t="s">
+      <c r="AG9" s="361" t="s">
         <v>51</v>
       </c>
-      <c r="AH9" s="335" t="s">
+      <c r="AH9" s="362" t="s">
         <v>52</v>
       </c>
-      <c r="AI9" s="335" t="s">
+      <c r="AI9" s="362" t="s">
         <v>53</v>
       </c>
-      <c r="AJ9" s="333" t="s">
+      <c r="AJ9" s="361" t="s">
         <v>54</v>
       </c>
-      <c r="AK9" s="328" t="s">
+      <c r="AK9" s="363" t="s">
         <v>55</v>
       </c>
-      <c r="AL9" s="331" t="s">
+      <c r="AL9" s="330" t="s">
         <v>56</v>
       </c>
-      <c r="AM9" s="333" t="s">
+      <c r="AM9" s="361" t="s">
         <v>57</v>
       </c>
-      <c r="AN9" s="334" t="s">
+      <c r="AN9" s="364" t="s">
         <v>58</v>
       </c>
-      <c r="AO9" s="331" t="s">
+      <c r="AO9" s="330" t="s">
         <v>59</v>
       </c>
-      <c r="AP9" s="332"/>
-      <c r="AQ9" s="332"/>
-      <c r="AR9" s="332"/>
-      <c r="AS9" s="332"/>
-      <c r="AT9" s="332"/>
-      <c r="AU9" s="332"/>
-      <c r="AV9" s="332"/>
-      <c r="AW9" s="332"/>
-      <c r="AX9" s="332"/>
-      <c r="AY9" s="324" t="s">
+      <c r="AP9" s="327"/>
+      <c r="AQ9" s="327"/>
+      <c r="AR9" s="327"/>
+      <c r="AS9" s="327"/>
+      <c r="AT9" s="327"/>
+      <c r="AU9" s="327"/>
+      <c r="AV9" s="327"/>
+      <c r="AW9" s="327"/>
+      <c r="AX9" s="327"/>
+      <c r="AY9" s="337" t="s">
         <v>21</v>
       </c>
-      <c r="AZ9" s="352"/>
-      <c r="BA9" s="352"/>
-      <c r="BB9" s="352"/>
-      <c r="BC9" s="352"/>
-      <c r="BD9" s="352"/>
-      <c r="BE9" s="352"/>
-      <c r="BF9" s="352"/>
-      <c r="BG9" s="352"/>
-      <c r="BH9" s="352"/>
-      <c r="BI9" s="352"/>
-      <c r="BJ9" s="353"/>
-      <c r="BK9" s="324" t="s">
+      <c r="AZ9" s="335"/>
+      <c r="BA9" s="335"/>
+      <c r="BB9" s="335"/>
+      <c r="BC9" s="335"/>
+      <c r="BD9" s="335"/>
+      <c r="BE9" s="335"/>
+      <c r="BF9" s="335"/>
+      <c r="BG9" s="335"/>
+      <c r="BH9" s="335"/>
+      <c r="BI9" s="335"/>
+      <c r="BJ9" s="336"/>
+      <c r="BK9" s="337" t="s">
         <v>60</v>
       </c>
-      <c r="BL9" s="352"/>
-      <c r="BM9" s="352"/>
-      <c r="BN9" s="352"/>
-      <c r="BO9" s="352"/>
-      <c r="BP9" s="353"/>
-      <c r="BQ9" s="355" t="s">
+      <c r="BL9" s="335"/>
+      <c r="BM9" s="335"/>
+      <c r="BN9" s="335"/>
+      <c r="BO9" s="335"/>
+      <c r="BP9" s="336"/>
+      <c r="BQ9" s="340" t="s">
         <v>61</v>
       </c>
-      <c r="BR9" s="355" t="s">
+      <c r="BR9" s="340" t="s">
         <v>62</v>
       </c>
-      <c r="BS9" s="332"/>
-      <c r="BT9" s="332"/>
-      <c r="BU9" s="329"/>
+      <c r="BS9" s="327"/>
+      <c r="BT9" s="327"/>
+      <c r="BU9" s="345"/>
       <c r="BV9" s="99"/>
-      <c r="BW9" s="344"/>
-      <c r="BX9" s="329"/>
-      <c r="BY9" s="348"/>
-      <c r="BZ9" s="348"/>
-      <c r="CA9" s="344"/>
-      <c r="CB9" s="332"/>
-      <c r="CC9" s="332"/>
-      <c r="CD9" s="332"/>
+      <c r="BW9" s="348"/>
+      <c r="BX9" s="345"/>
+      <c r="BY9" s="352"/>
+      <c r="BZ9" s="352"/>
+      <c r="CA9" s="348"/>
+      <c r="CB9" s="327"/>
+      <c r="CC9" s="327"/>
+      <c r="CD9" s="327"/>
       <c r="CH9" s="16"/>
       <c r="CI9" s="17"/>
     </row>
     <row r="10" spans="1:87" s="18" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="332"/>
-      <c r="B10" s="332"/>
-      <c r="C10" s="332"/>
-      <c r="D10" s="332"/>
-      <c r="E10" s="332"/>
-      <c r="F10" s="332"/>
-      <c r="G10" s="332"/>
-      <c r="H10" s="332"/>
-      <c r="I10" s="332"/>
-      <c r="J10" s="332"/>
-      <c r="K10" s="332"/>
-      <c r="L10" s="332"/>
-      <c r="M10" s="332"/>
-      <c r="N10" s="332"/>
-      <c r="O10" s="332"/>
-      <c r="P10" s="332"/>
-      <c r="Q10" s="332"/>
-      <c r="R10" s="332"/>
-      <c r="S10" s="332"/>
-      <c r="T10" s="332"/>
-      <c r="U10" s="332"/>
-      <c r="V10" s="330"/>
-      <c r="W10" s="341"/>
-      <c r="X10" s="332"/>
-      <c r="Y10" s="332"/>
-      <c r="Z10" s="332"/>
-      <c r="AA10" s="332"/>
-      <c r="AB10" s="332"/>
-      <c r="AC10" s="332"/>
-      <c r="AD10" s="332"/>
-      <c r="AE10" s="332"/>
-      <c r="AF10" s="332"/>
-      <c r="AG10" s="332"/>
-      <c r="AH10" s="332"/>
-      <c r="AI10" s="332"/>
-      <c r="AJ10" s="332"/>
-      <c r="AK10" s="329"/>
-      <c r="AL10" s="332"/>
-      <c r="AM10" s="332"/>
-      <c r="AN10" s="332"/>
-      <c r="AO10" s="332"/>
-      <c r="AP10" s="332"/>
-      <c r="AQ10" s="332"/>
-      <c r="AR10" s="332"/>
-      <c r="AS10" s="332"/>
-      <c r="AT10" s="332"/>
-      <c r="AU10" s="332"/>
-      <c r="AV10" s="332"/>
-      <c r="AW10" s="332"/>
-      <c r="AX10" s="332"/>
+      <c r="A10" s="327"/>
+      <c r="B10" s="327"/>
+      <c r="C10" s="327"/>
+      <c r="D10" s="327"/>
+      <c r="E10" s="327"/>
+      <c r="F10" s="327"/>
+      <c r="G10" s="327"/>
+      <c r="H10" s="327"/>
+      <c r="I10" s="327"/>
+      <c r="J10" s="327"/>
+      <c r="K10" s="327"/>
+      <c r="L10" s="327"/>
+      <c r="M10" s="327"/>
+      <c r="N10" s="327"/>
+      <c r="O10" s="327"/>
+      <c r="P10" s="327"/>
+      <c r="Q10" s="327"/>
+      <c r="R10" s="327"/>
+      <c r="S10" s="327"/>
+      <c r="T10" s="327"/>
+      <c r="U10" s="327"/>
+      <c r="V10" s="346"/>
+      <c r="W10" s="360"/>
+      <c r="X10" s="327"/>
+      <c r="Y10" s="327"/>
+      <c r="Z10" s="327"/>
+      <c r="AA10" s="327"/>
+      <c r="AB10" s="327"/>
+      <c r="AC10" s="327"/>
+      <c r="AD10" s="327"/>
+      <c r="AE10" s="327"/>
+      <c r="AF10" s="327"/>
+      <c r="AG10" s="327"/>
+      <c r="AH10" s="327"/>
+      <c r="AI10" s="327"/>
+      <c r="AJ10" s="327"/>
+      <c r="AK10" s="345"/>
+      <c r="AL10" s="327"/>
+      <c r="AM10" s="327"/>
+      <c r="AN10" s="327"/>
+      <c r="AO10" s="327"/>
+      <c r="AP10" s="327"/>
+      <c r="AQ10" s="327"/>
+      <c r="AR10" s="327"/>
+      <c r="AS10" s="327"/>
+      <c r="AT10" s="327"/>
+      <c r="AU10" s="327"/>
+      <c r="AV10" s="327"/>
+      <c r="AW10" s="327"/>
+      <c r="AX10" s="327"/>
       <c r="AY10" s="88" t="s">
         <v>63</v>
       </c>
@@ -15332,123 +15333,123 @@
       <c r="BA10" s="88" t="s">
         <v>65</v>
       </c>
-      <c r="BB10" s="369" t="s">
+      <c r="BB10" s="371" t="s">
         <v>66</v>
       </c>
-      <c r="BC10" s="367" t="s">
+      <c r="BC10" s="370" t="s">
         <v>67</v>
       </c>
-      <c r="BD10" s="367" t="s">
+      <c r="BD10" s="370" t="s">
         <v>68</v>
       </c>
-      <c r="BE10" s="367" t="s">
+      <c r="BE10" s="370" t="s">
         <v>121</v>
       </c>
-      <c r="BF10" s="367" t="s">
+      <c r="BF10" s="370" t="s">
         <v>70</v>
       </c>
-      <c r="BG10" s="367" t="s">
+      <c r="BG10" s="370" t="s">
         <v>71</v>
       </c>
-      <c r="BH10" s="367" t="s">
+      <c r="BH10" s="370" t="s">
         <v>72</v>
       </c>
-      <c r="BI10" s="367" t="s">
+      <c r="BI10" s="370" t="s">
         <v>75</v>
       </c>
-      <c r="BJ10" s="368" t="s">
+      <c r="BJ10" s="373" t="s">
         <v>76</v>
       </c>
-      <c r="BK10" s="367" t="s">
+      <c r="BK10" s="370" t="s">
         <v>77</v>
       </c>
-      <c r="BL10" s="366" t="s">
+      <c r="BL10" s="372" t="s">
         <v>78</v>
       </c>
-      <c r="BM10" s="367" t="s">
+      <c r="BM10" s="370" t="s">
         <v>79</v>
       </c>
-      <c r="BN10" s="366" t="s">
+      <c r="BN10" s="372" t="s">
         <v>80</v>
       </c>
-      <c r="BO10" s="366" t="s">
+      <c r="BO10" s="372" t="s">
         <v>122</v>
       </c>
-      <c r="BP10" s="324" t="s">
+      <c r="BP10" s="337" t="s">
         <v>81</v>
       </c>
-      <c r="BQ10" s="332"/>
-      <c r="BR10" s="332"/>
-      <c r="BS10" s="332"/>
-      <c r="BT10" s="332"/>
-      <c r="BU10" s="329"/>
+      <c r="BQ10" s="327"/>
+      <c r="BR10" s="327"/>
+      <c r="BS10" s="327"/>
+      <c r="BT10" s="327"/>
+      <c r="BU10" s="345"/>
       <c r="BV10" s="99"/>
-      <c r="BW10" s="344"/>
-      <c r="BX10" s="349"/>
-      <c r="BY10" s="350"/>
-      <c r="BZ10" s="350"/>
-      <c r="CA10" s="345"/>
-      <c r="CB10" s="332"/>
-      <c r="CC10" s="332"/>
-      <c r="CD10" s="332"/>
+      <c r="BW10" s="348"/>
+      <c r="BX10" s="353"/>
+      <c r="BY10" s="354"/>
+      <c r="BZ10" s="354"/>
+      <c r="CA10" s="349"/>
+      <c r="CB10" s="327"/>
+      <c r="CC10" s="327"/>
+      <c r="CD10" s="327"/>
       <c r="CH10" s="16"/>
       <c r="CI10" s="17"/>
     </row>
     <row r="11" spans="1:87" s="18" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A11" s="325"/>
-      <c r="B11" s="325"/>
-      <c r="C11" s="325"/>
-      <c r="D11" s="325"/>
-      <c r="E11" s="325"/>
-      <c r="F11" s="325"/>
-      <c r="G11" s="325"/>
-      <c r="H11" s="325"/>
-      <c r="I11" s="325"/>
-      <c r="J11" s="325"/>
-      <c r="K11" s="325"/>
-      <c r="L11" s="325"/>
-      <c r="M11" s="325"/>
-      <c r="N11" s="325"/>
-      <c r="O11" s="325"/>
-      <c r="P11" s="325"/>
-      <c r="Q11" s="325"/>
-      <c r="R11" s="325"/>
-      <c r="S11" s="325"/>
-      <c r="T11" s="325"/>
-      <c r="U11" s="325"/>
+      <c r="A11" s="328"/>
+      <c r="B11" s="328"/>
+      <c r="C11" s="328"/>
+      <c r="D11" s="328"/>
+      <c r="E11" s="328"/>
+      <c r="F11" s="328"/>
+      <c r="G11" s="328"/>
+      <c r="H11" s="328"/>
+      <c r="I11" s="328"/>
+      <c r="J11" s="328"/>
+      <c r="K11" s="328"/>
+      <c r="L11" s="328"/>
+      <c r="M11" s="328"/>
+      <c r="N11" s="328"/>
+      <c r="O11" s="328"/>
+      <c r="P11" s="328"/>
+      <c r="Q11" s="328"/>
+      <c r="R11" s="328"/>
+      <c r="S11" s="328"/>
+      <c r="T11" s="328"/>
+      <c r="U11" s="328"/>
       <c r="V11" s="19" t="s">
         <v>82</v>
       </c>
       <c r="W11" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="X11" s="325"/>
-      <c r="Y11" s="325"/>
-      <c r="Z11" s="325"/>
-      <c r="AA11" s="325"/>
-      <c r="AB11" s="325"/>
-      <c r="AC11" s="325"/>
-      <c r="AD11" s="325"/>
-      <c r="AE11" s="325"/>
-      <c r="AF11" s="325"/>
-      <c r="AG11" s="325"/>
-      <c r="AH11" s="325"/>
-      <c r="AI11" s="325"/>
-      <c r="AJ11" s="325"/>
-      <c r="AK11" s="330"/>
-      <c r="AL11" s="325"/>
-      <c r="AM11" s="325"/>
-      <c r="AN11" s="325"/>
-      <c r="AO11" s="325"/>
-      <c r="AP11" s="325"/>
-      <c r="AQ11" s="325"/>
-      <c r="AR11" s="325"/>
-      <c r="AS11" s="325"/>
-      <c r="AT11" s="325"/>
-      <c r="AU11" s="325"/>
-      <c r="AV11" s="325"/>
-      <c r="AW11" s="325"/>
-      <c r="AX11" s="325"/>
+      <c r="X11" s="328"/>
+      <c r="Y11" s="328"/>
+      <c r="Z11" s="328"/>
+      <c r="AA11" s="328"/>
+      <c r="AB11" s="328"/>
+      <c r="AC11" s="328"/>
+      <c r="AD11" s="328"/>
+      <c r="AE11" s="328"/>
+      <c r="AF11" s="328"/>
+      <c r="AG11" s="328"/>
+      <c r="AH11" s="328"/>
+      <c r="AI11" s="328"/>
+      <c r="AJ11" s="328"/>
+      <c r="AK11" s="346"/>
+      <c r="AL11" s="328"/>
+      <c r="AM11" s="328"/>
+      <c r="AN11" s="328"/>
+      <c r="AO11" s="328"/>
+      <c r="AP11" s="328"/>
+      <c r="AQ11" s="328"/>
+      <c r="AR11" s="328"/>
+      <c r="AS11" s="328"/>
+      <c r="AT11" s="328"/>
+      <c r="AU11" s="328"/>
+      <c r="AV11" s="328"/>
+      <c r="AW11" s="328"/>
+      <c r="AX11" s="328"/>
       <c r="AY11" s="89" t="s">
         <v>84</v>
       </c>
@@ -15458,28 +15459,28 @@
       <c r="BA11" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="BB11" s="325"/>
-      <c r="BC11" s="325"/>
-      <c r="BD11" s="325"/>
-      <c r="BE11" s="325"/>
-      <c r="BF11" s="325"/>
-      <c r="BG11" s="325"/>
-      <c r="BH11" s="325"/>
-      <c r="BI11" s="325"/>
-      <c r="BJ11" s="325"/>
-      <c r="BK11" s="325"/>
-      <c r="BL11" s="325"/>
-      <c r="BM11" s="325"/>
-      <c r="BN11" s="325"/>
-      <c r="BO11" s="325"/>
-      <c r="BP11" s="325"/>
-      <c r="BQ11" s="325"/>
-      <c r="BR11" s="325"/>
-      <c r="BS11" s="325"/>
-      <c r="BT11" s="325"/>
-      <c r="BU11" s="330"/>
+      <c r="BB11" s="328"/>
+      <c r="BC11" s="328"/>
+      <c r="BD11" s="328"/>
+      <c r="BE11" s="328"/>
+      <c r="BF11" s="328"/>
+      <c r="BG11" s="328"/>
+      <c r="BH11" s="328"/>
+      <c r="BI11" s="328"/>
+      <c r="BJ11" s="328"/>
+      <c r="BK11" s="328"/>
+      <c r="BL11" s="328"/>
+      <c r="BM11" s="328"/>
+      <c r="BN11" s="328"/>
+      <c r="BO11" s="328"/>
+      <c r="BP11" s="328"/>
+      <c r="BQ11" s="328"/>
+      <c r="BR11" s="328"/>
+      <c r="BS11" s="328"/>
+      <c r="BT11" s="328"/>
+      <c r="BU11" s="346"/>
       <c r="BV11" s="99"/>
-      <c r="BW11" s="345"/>
+      <c r="BW11" s="349"/>
       <c r="BX11" s="61" t="s">
         <v>87</v>
       </c>
@@ -15492,9 +15493,9 @@
       <c r="CA11" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="CB11" s="337"/>
-      <c r="CC11" s="337"/>
-      <c r="CD11" s="337"/>
+      <c r="CB11" s="356"/>
+      <c r="CC11" s="356"/>
+      <c r="CD11" s="356"/>
       <c r="CE11" s="2"/>
       <c r="CF11" s="20"/>
       <c r="CH11" s="16"/>
@@ -17894,6 +17895,72 @@
     </row>
   </sheetData>
   <mergeCells count="82">
+    <mergeCell ref="AJ9:AJ11"/>
+    <mergeCell ref="AK9:AK11"/>
+    <mergeCell ref="BQ9:BQ11"/>
+    <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BC10:BC11"/>
+    <mergeCell ref="BD10:BD11"/>
+    <mergeCell ref="BE10:BE11"/>
+    <mergeCell ref="AM9:AM11"/>
+    <mergeCell ref="AN9:AN11"/>
+    <mergeCell ref="AO9:AO11"/>
+    <mergeCell ref="AY9:BJ9"/>
+    <mergeCell ref="BK9:BP9"/>
+    <mergeCell ref="BO10:BO11"/>
+    <mergeCell ref="BP10:BP11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="T9:T11"/>
+    <mergeCell ref="U9:U11"/>
+    <mergeCell ref="V9:W10"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="Y9:Y11"/>
+    <mergeCell ref="BX8:CA10"/>
+    <mergeCell ref="CB8:CB11"/>
+    <mergeCell ref="CC8:CC11"/>
+    <mergeCell ref="AR8:AR11"/>
+    <mergeCell ref="AS8:AS11"/>
+    <mergeCell ref="AT8:AT11"/>
+    <mergeCell ref="AU8:AU11"/>
+    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="AW8:AW11"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BL10:BL11"/>
+    <mergeCell ref="BM10:BM11"/>
+    <mergeCell ref="BN10:BN11"/>
+    <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="BG10:BG11"/>
+    <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="Z9:Z11"/>
+    <mergeCell ref="BW8:BW11"/>
+    <mergeCell ref="AQ8:AQ11"/>
+    <mergeCell ref="AL9:AL11"/>
+    <mergeCell ref="AA9:AA11"/>
+    <mergeCell ref="AB9:AB11"/>
+    <mergeCell ref="AC9:AC11"/>
+    <mergeCell ref="AD9:AD11"/>
+    <mergeCell ref="AE9:AE11"/>
+    <mergeCell ref="AF9:AF11"/>
+    <mergeCell ref="AG9:AG11"/>
+    <mergeCell ref="AH9:AH11"/>
+    <mergeCell ref="AI9:AI11"/>
+    <mergeCell ref="Q9:Q11"/>
+    <mergeCell ref="R9:R11"/>
+    <mergeCell ref="S9:S11"/>
+    <mergeCell ref="CD8:CD11"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="O9:O11"/>
+    <mergeCell ref="AX8:AX11"/>
+    <mergeCell ref="AY8:BP8"/>
+    <mergeCell ref="BQ8:BR8"/>
+    <mergeCell ref="BS8:BS11"/>
+    <mergeCell ref="BT8:BT11"/>
+    <mergeCell ref="BU8:BU11"/>
+    <mergeCell ref="BR9:BR11"/>
     <mergeCell ref="A3:BU3"/>
     <mergeCell ref="BW3:CB6"/>
     <mergeCell ref="A8:A11"/>
@@ -17910,72 +17977,6 @@
     <mergeCell ref="Y8:AO8"/>
     <mergeCell ref="AP8:AP11"/>
     <mergeCell ref="P9:P11"/>
-    <mergeCell ref="Q9:Q11"/>
-    <mergeCell ref="R9:R11"/>
-    <mergeCell ref="S9:S11"/>
-    <mergeCell ref="CD8:CD11"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="O9:O11"/>
-    <mergeCell ref="AX8:AX11"/>
-    <mergeCell ref="AY8:BP8"/>
-    <mergeCell ref="BQ8:BR8"/>
-    <mergeCell ref="BS8:BS11"/>
-    <mergeCell ref="BT8:BT11"/>
-    <mergeCell ref="BU8:BU11"/>
-    <mergeCell ref="BR9:BR11"/>
-    <mergeCell ref="BF10:BF11"/>
-    <mergeCell ref="BG10:BG11"/>
-    <mergeCell ref="BH10:BH11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="BW8:BW11"/>
-    <mergeCell ref="BX8:CA10"/>
-    <mergeCell ref="CB8:CB11"/>
-    <mergeCell ref="CC8:CC11"/>
-    <mergeCell ref="AR8:AR11"/>
-    <mergeCell ref="AS8:AS11"/>
-    <mergeCell ref="AT8:AT11"/>
-    <mergeCell ref="AU8:AU11"/>
-    <mergeCell ref="AV8:AV11"/>
-    <mergeCell ref="AW8:AW11"/>
-    <mergeCell ref="AQ8:AQ11"/>
-    <mergeCell ref="T9:T11"/>
-    <mergeCell ref="U9:U11"/>
-    <mergeCell ref="V9:W10"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="Y9:Y11"/>
-    <mergeCell ref="AL9:AL11"/>
-    <mergeCell ref="AA9:AA11"/>
-    <mergeCell ref="AB9:AB11"/>
-    <mergeCell ref="AC9:AC11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="AE9:AE11"/>
-    <mergeCell ref="AF9:AF11"/>
-    <mergeCell ref="AG9:AG11"/>
-    <mergeCell ref="AH9:AH11"/>
-    <mergeCell ref="AI9:AI11"/>
-    <mergeCell ref="AJ9:AJ11"/>
-    <mergeCell ref="AK9:AK11"/>
-    <mergeCell ref="BQ9:BQ11"/>
-    <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BC10:BC11"/>
-    <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BE10:BE11"/>
-    <mergeCell ref="AM9:AM11"/>
-    <mergeCell ref="AN9:AN11"/>
-    <mergeCell ref="AO9:AO11"/>
-    <mergeCell ref="AY9:BJ9"/>
-    <mergeCell ref="BK9:BP9"/>
-    <mergeCell ref="BO10:BO11"/>
-    <mergeCell ref="BP10:BP11"/>
-    <mergeCell ref="BI10:BI11"/>
-    <mergeCell ref="BJ10:BJ11"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BL10:BL11"/>
-    <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BN10:BN11"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B7 B22:B1048576 B12:BU12">
     <cfRule type="duplicateValues" dxfId="17" priority="8"/>
@@ -17988,8 +17989,8 @@
     <cfRule type="duplicateValues" dxfId="14" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:B21">
-    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
     <cfRule type="duplicateValues" dxfId="11" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="BJ13">
@@ -18174,91 +18175,91 @@
       <c r="CD2" s="235"/>
     </row>
     <row r="3" spans="1:87" s="236" customFormat="1" outlineLevel="1">
-      <c r="A3" s="359" t="str">
+      <c r="A3" s="324" t="str">
         <f ca="1">"BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …."&amp;" NĂM "&amp;YEAR(NOW())</f>
         <v>BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …. NĂM 2026</v>
       </c>
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
-      <c r="M3" s="359"/>
-      <c r="N3" s="359"/>
-      <c r="O3" s="359"/>
-      <c r="P3" s="359"/>
-      <c r="Q3" s="359"/>
-      <c r="R3" s="359"/>
-      <c r="S3" s="359"/>
-      <c r="T3" s="359"/>
-      <c r="U3" s="359"/>
-      <c r="V3" s="359"/>
-      <c r="W3" s="359"/>
-      <c r="X3" s="359"/>
-      <c r="Y3" s="359"/>
-      <c r="Z3" s="359"/>
-      <c r="AA3" s="359"/>
-      <c r="AB3" s="359"/>
-      <c r="AC3" s="359"/>
-      <c r="AD3" s="359"/>
-      <c r="AE3" s="359"/>
-      <c r="AF3" s="359"/>
-      <c r="AG3" s="359"/>
-      <c r="AH3" s="359"/>
-      <c r="AI3" s="359"/>
-      <c r="AJ3" s="359"/>
-      <c r="AK3" s="359"/>
-      <c r="AL3" s="359"/>
-      <c r="AM3" s="359"/>
-      <c r="AN3" s="359"/>
-      <c r="AO3" s="359"/>
-      <c r="AP3" s="359"/>
-      <c r="AQ3" s="359"/>
-      <c r="AR3" s="359"/>
-      <c r="AS3" s="359"/>
-      <c r="AT3" s="359"/>
-      <c r="AU3" s="359"/>
-      <c r="AV3" s="359"/>
-      <c r="AW3" s="359"/>
-      <c r="AX3" s="359"/>
-      <c r="AY3" s="359"/>
-      <c r="AZ3" s="359"/>
-      <c r="BA3" s="359"/>
-      <c r="BB3" s="359"/>
-      <c r="BC3" s="359"/>
-      <c r="BD3" s="359"/>
-      <c r="BE3" s="359"/>
-      <c r="BF3" s="359"/>
-      <c r="BG3" s="359"/>
-      <c r="BH3" s="359"/>
-      <c r="BI3" s="359"/>
-      <c r="BJ3" s="359"/>
-      <c r="BK3" s="359"/>
-      <c r="BL3" s="359"/>
-      <c r="BM3" s="359"/>
-      <c r="BN3" s="359"/>
-      <c r="BO3" s="359"/>
-      <c r="BP3" s="359"/>
-      <c r="BQ3" s="359"/>
-      <c r="BR3" s="359"/>
-      <c r="BS3" s="359"/>
-      <c r="BT3" s="359"/>
-      <c r="BU3" s="359"/>
+      <c r="B3" s="324"/>
+      <c r="C3" s="324"/>
+      <c r="D3" s="324"/>
+      <c r="E3" s="324"/>
+      <c r="F3" s="324"/>
+      <c r="G3" s="324"/>
+      <c r="H3" s="324"/>
+      <c r="I3" s="324"/>
+      <c r="J3" s="324"/>
+      <c r="K3" s="324"/>
+      <c r="L3" s="324"/>
+      <c r="M3" s="324"/>
+      <c r="N3" s="324"/>
+      <c r="O3" s="324"/>
+      <c r="P3" s="324"/>
+      <c r="Q3" s="324"/>
+      <c r="R3" s="324"/>
+      <c r="S3" s="324"/>
+      <c r="T3" s="324"/>
+      <c r="U3" s="324"/>
+      <c r="V3" s="324"/>
+      <c r="W3" s="324"/>
+      <c r="X3" s="324"/>
+      <c r="Y3" s="324"/>
+      <c r="Z3" s="324"/>
+      <c r="AA3" s="324"/>
+      <c r="AB3" s="324"/>
+      <c r="AC3" s="324"/>
+      <c r="AD3" s="324"/>
+      <c r="AE3" s="324"/>
+      <c r="AF3" s="324"/>
+      <c r="AG3" s="324"/>
+      <c r="AH3" s="324"/>
+      <c r="AI3" s="324"/>
+      <c r="AJ3" s="324"/>
+      <c r="AK3" s="324"/>
+      <c r="AL3" s="324"/>
+      <c r="AM3" s="324"/>
+      <c r="AN3" s="324"/>
+      <c r="AO3" s="324"/>
+      <c r="AP3" s="324"/>
+      <c r="AQ3" s="324"/>
+      <c r="AR3" s="324"/>
+      <c r="AS3" s="324"/>
+      <c r="AT3" s="324"/>
+      <c r="AU3" s="324"/>
+      <c r="AV3" s="324"/>
+      <c r="AW3" s="324"/>
+      <c r="AX3" s="324"/>
+      <c r="AY3" s="324"/>
+      <c r="AZ3" s="324"/>
+      <c r="BA3" s="324"/>
+      <c r="BB3" s="324"/>
+      <c r="BC3" s="324"/>
+      <c r="BD3" s="324"/>
+      <c r="BE3" s="324"/>
+      <c r="BF3" s="324"/>
+      <c r="BG3" s="324"/>
+      <c r="BH3" s="324"/>
+      <c r="BI3" s="324"/>
+      <c r="BJ3" s="324"/>
+      <c r="BK3" s="324"/>
+      <c r="BL3" s="324"/>
+      <c r="BM3" s="324"/>
+      <c r="BN3" s="324"/>
+      <c r="BO3" s="324"/>
+      <c r="BP3" s="324"/>
+      <c r="BQ3" s="324"/>
+      <c r="BR3" s="324"/>
+      <c r="BS3" s="324"/>
+      <c r="BT3" s="324"/>
+      <c r="BU3" s="324"/>
       <c r="BV3"/>
-      <c r="BW3" s="360" t="s">
+      <c r="BW3" s="325" t="s">
         <v>131</v>
       </c>
-      <c r="BX3" s="360"/>
-      <c r="BY3" s="360"/>
-      <c r="BZ3" s="360"/>
-      <c r="CA3" s="360"/>
-      <c r="CB3" s="359"/>
+      <c r="BX3" s="325"/>
+      <c r="BY3" s="325"/>
+      <c r="BZ3" s="325"/>
+      <c r="CA3" s="325"/>
+      <c r="CB3" s="324"/>
       <c r="CC3" s="110"/>
       <c r="CD3" s="110"/>
       <c r="CE3" s="236" t="s">
@@ -18342,366 +18343,366 @@
       <c r="BT4" s="237"/>
       <c r="BU4" s="237"/>
       <c r="BV4"/>
-      <c r="BW4" s="359"/>
-      <c r="BX4" s="359"/>
-      <c r="BY4" s="359"/>
-      <c r="BZ4" s="359"/>
-      <c r="CA4" s="359"/>
-      <c r="CB4" s="359"/>
+      <c r="BW4" s="324"/>
+      <c r="BX4" s="324"/>
+      <c r="BY4" s="324"/>
+      <c r="BZ4" s="324"/>
+      <c r="CA4" s="324"/>
+      <c r="CB4" s="324"/>
       <c r="CC4" s="110"/>
       <c r="CD4" s="110"/>
     </row>
     <row r="5" spans="1:87" s="111" customFormat="1" ht="11">
-      <c r="A5" s="424" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="427" t="s">
+      <c r="A5" s="374" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="377" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="378" t="s">
+      <c r="C5" s="380" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="430" t="s">
+      <c r="D5" s="383" t="s">
         <v>117</v>
       </c>
-      <c r="E5" s="430" t="s">
+      <c r="E5" s="383" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="433" t="s">
+      <c r="F5" s="386" t="s">
         <v>118</v>
       </c>
-      <c r="G5" s="378" t="s">
+      <c r="G5" s="380" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="387" t="s">
+      <c r="H5" s="389" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="387" t="s">
+      <c r="I5" s="389" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="378" t="s">
+      <c r="J5" s="380" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="419" t="s">
+      <c r="K5" s="392" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="420"/>
-      <c r="M5" s="420"/>
-      <c r="N5" s="420"/>
-      <c r="O5" s="420"/>
-      <c r="P5" s="420"/>
-      <c r="Q5" s="420"/>
-      <c r="R5" s="420"/>
-      <c r="S5" s="420"/>
-      <c r="T5" s="420"/>
-      <c r="U5" s="420"/>
-      <c r="V5" s="420"/>
-      <c r="W5" s="420"/>
-      <c r="X5" s="421"/>
-      <c r="Y5" s="328" t="s">
+      <c r="L5" s="393"/>
+      <c r="M5" s="393"/>
+      <c r="N5" s="393"/>
+      <c r="O5" s="393"/>
+      <c r="P5" s="393"/>
+      <c r="Q5" s="393"/>
+      <c r="R5" s="393"/>
+      <c r="S5" s="393"/>
+      <c r="T5" s="393"/>
+      <c r="U5" s="393"/>
+      <c r="V5" s="393"/>
+      <c r="W5" s="393"/>
+      <c r="X5" s="394"/>
+      <c r="Y5" s="363" t="s">
         <v>11</v>
       </c>
-      <c r="Z5" s="422"/>
-      <c r="AA5" s="422"/>
-      <c r="AB5" s="422"/>
-      <c r="AC5" s="422"/>
-      <c r="AD5" s="422"/>
-      <c r="AE5" s="422"/>
-      <c r="AF5" s="422"/>
-      <c r="AG5" s="422"/>
-      <c r="AH5" s="422"/>
-      <c r="AI5" s="422"/>
-      <c r="AJ5" s="422"/>
-      <c r="AK5" s="422"/>
-      <c r="AL5" s="422"/>
-      <c r="AM5" s="422"/>
-      <c r="AN5" s="422"/>
-      <c r="AO5" s="423"/>
-      <c r="AP5" s="378" t="s">
+      <c r="Z5" s="395"/>
+      <c r="AA5" s="395"/>
+      <c r="AB5" s="395"/>
+      <c r="AC5" s="395"/>
+      <c r="AD5" s="395"/>
+      <c r="AE5" s="395"/>
+      <c r="AF5" s="395"/>
+      <c r="AG5" s="395"/>
+      <c r="AH5" s="395"/>
+      <c r="AI5" s="395"/>
+      <c r="AJ5" s="395"/>
+      <c r="AK5" s="395"/>
+      <c r="AL5" s="395"/>
+      <c r="AM5" s="395"/>
+      <c r="AN5" s="395"/>
+      <c r="AO5" s="396"/>
+      <c r="AP5" s="380" t="s">
         <v>12</v>
       </c>
-      <c r="AQ5" s="378" t="s">
+      <c r="AQ5" s="380" t="s">
         <v>13</v>
       </c>
-      <c r="AR5" s="378" t="s">
+      <c r="AR5" s="380" t="s">
         <v>14</v>
       </c>
-      <c r="AS5" s="378" t="s">
+      <c r="AS5" s="380" t="s">
         <v>15</v>
       </c>
-      <c r="AT5" s="378" t="s">
+      <c r="AT5" s="380" t="s">
         <v>16</v>
       </c>
-      <c r="AU5" s="378" t="s">
+      <c r="AU5" s="380" t="s">
         <v>17</v>
       </c>
-      <c r="AV5" s="378" t="s">
+      <c r="AV5" s="380" t="s">
         <v>18</v>
       </c>
-      <c r="AW5" s="378" t="s">
+      <c r="AW5" s="380" t="s">
         <v>19</v>
       </c>
-      <c r="AX5" s="378" t="s">
+      <c r="AX5" s="380" t="s">
         <v>20</v>
       </c>
-      <c r="AY5" s="342" t="s">
+      <c r="AY5" s="344" t="s">
         <v>21</v>
       </c>
-      <c r="AZ5" s="384"/>
-      <c r="BA5" s="384"/>
-      <c r="BB5" s="384"/>
-      <c r="BC5" s="384"/>
-      <c r="BD5" s="384"/>
-      <c r="BE5" s="384"/>
-      <c r="BF5" s="384"/>
-      <c r="BG5" s="384"/>
-      <c r="BH5" s="384"/>
-      <c r="BI5" s="384"/>
-      <c r="BJ5" s="384"/>
-      <c r="BK5" s="384"/>
-      <c r="BL5" s="384"/>
-      <c r="BM5" s="384"/>
-      <c r="BN5" s="384"/>
-      <c r="BO5" s="384"/>
-      <c r="BP5" s="385"/>
-      <c r="BQ5" s="415" t="s">
+      <c r="AZ5" s="403"/>
+      <c r="BA5" s="403"/>
+      <c r="BB5" s="403"/>
+      <c r="BC5" s="403"/>
+      <c r="BD5" s="403"/>
+      <c r="BE5" s="403"/>
+      <c r="BF5" s="403"/>
+      <c r="BG5" s="403"/>
+      <c r="BH5" s="403"/>
+      <c r="BI5" s="403"/>
+      <c r="BJ5" s="403"/>
+      <c r="BK5" s="403"/>
+      <c r="BL5" s="403"/>
+      <c r="BM5" s="403"/>
+      <c r="BN5" s="403"/>
+      <c r="BO5" s="403"/>
+      <c r="BP5" s="404"/>
+      <c r="BQ5" s="405" t="s">
         <v>22</v>
       </c>
-      <c r="BR5" s="416"/>
-      <c r="BS5" s="354" t="s">
+      <c r="BR5" s="406"/>
+      <c r="BS5" s="338" t="s">
         <v>119</v>
       </c>
-      <c r="BT5" s="354" t="s">
+      <c r="BT5" s="338" t="s">
         <v>23</v>
       </c>
-      <c r="BU5" s="415" t="s">
+      <c r="BU5" s="405" t="s">
         <v>24</v>
       </c>
-      <c r="BW5" s="397" t="s">
+      <c r="BW5" s="412" t="s">
         <v>25</v>
       </c>
-      <c r="BX5" s="400" t="s">
+      <c r="BX5" s="415" t="s">
         <v>26</v>
       </c>
-      <c r="BY5" s="401"/>
-      <c r="BZ5" s="401"/>
-      <c r="CA5" s="402"/>
-      <c r="CB5" s="409" t="s">
+      <c r="BY5" s="416"/>
+      <c r="BZ5" s="416"/>
+      <c r="CA5" s="417"/>
+      <c r="CB5" s="424" t="s">
         <v>27</v>
       </c>
-      <c r="CC5" s="412" t="s">
+      <c r="CC5" s="400" t="s">
         <v>28</v>
       </c>
-      <c r="CD5" s="412" t="s">
+      <c r="CD5" s="400" t="s">
         <v>29</v>
       </c>
       <c r="CH5" s="112"/>
       <c r="CI5" s="113"/>
     </row>
     <row r="6" spans="1:87" s="111" customFormat="1" ht="11">
-      <c r="A6" s="425"/>
-      <c r="B6" s="428"/>
-      <c r="C6" s="379"/>
-      <c r="D6" s="431"/>
-      <c r="E6" s="431"/>
-      <c r="F6" s="434"/>
-      <c r="G6" s="379"/>
-      <c r="H6" s="388"/>
-      <c r="I6" s="388"/>
-      <c r="J6" s="379"/>
-      <c r="K6" s="390" t="s">
+      <c r="A6" s="375"/>
+      <c r="B6" s="378"/>
+      <c r="C6" s="381"/>
+      <c r="D6" s="384"/>
+      <c r="E6" s="384"/>
+      <c r="F6" s="387"/>
+      <c r="G6" s="381"/>
+      <c r="H6" s="390"/>
+      <c r="I6" s="390"/>
+      <c r="J6" s="381"/>
+      <c r="K6" s="397" t="s">
         <v>30</v>
       </c>
-      <c r="L6" s="390" t="s">
+      <c r="L6" s="397" t="s">
         <v>31</v>
       </c>
-      <c r="M6" s="390" t="s">
+      <c r="M6" s="397" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="390" t="s">
+      <c r="N6" s="397" t="s">
         <v>33</v>
       </c>
-      <c r="O6" s="390" t="s">
+      <c r="O6" s="397" t="s">
         <v>34</v>
       </c>
-      <c r="P6" s="390" t="s">
+      <c r="P6" s="397" t="s">
         <v>35</v>
       </c>
-      <c r="Q6" s="390" t="s">
+      <c r="Q6" s="397" t="s">
         <v>36</v>
       </c>
-      <c r="R6" s="390" t="s">
+      <c r="R6" s="397" t="s">
         <v>37</v>
       </c>
-      <c r="S6" s="390" t="s">
+      <c r="S6" s="397" t="s">
         <v>38</v>
       </c>
-      <c r="T6" s="390" t="s">
+      <c r="T6" s="397" t="s">
         <v>39</v>
       </c>
-      <c r="U6" s="390" t="s">
+      <c r="U6" s="397" t="s">
         <v>40</v>
       </c>
-      <c r="V6" s="393" t="s">
+      <c r="V6" s="427" t="s">
         <v>41</v>
       </c>
-      <c r="W6" s="394"/>
-      <c r="X6" s="390" t="s">
+      <c r="W6" s="428"/>
+      <c r="X6" s="397" t="s">
         <v>42</v>
       </c>
-      <c r="Y6" s="378" t="s">
+      <c r="Y6" s="380" t="s">
         <v>43</v>
       </c>
-      <c r="Z6" s="378" t="s">
+      <c r="Z6" s="380" t="s">
         <v>44</v>
       </c>
-      <c r="AA6" s="378" t="s">
+      <c r="AA6" s="380" t="s">
         <v>45</v>
       </c>
-      <c r="AB6" s="378" t="s">
+      <c r="AB6" s="380" t="s">
         <v>46</v>
       </c>
-      <c r="AC6" s="387" t="s">
+      <c r="AC6" s="389" t="s">
         <v>47</v>
       </c>
-      <c r="AD6" s="387" t="s">
+      <c r="AD6" s="389" t="s">
         <v>120</v>
       </c>
-      <c r="AE6" s="387" t="s">
+      <c r="AE6" s="389" t="s">
         <v>49</v>
       </c>
-      <c r="AF6" s="387" t="s">
+      <c r="AF6" s="389" t="s">
         <v>50</v>
       </c>
-      <c r="AG6" s="378" t="s">
+      <c r="AG6" s="380" t="s">
         <v>51</v>
       </c>
-      <c r="AH6" s="387" t="s">
+      <c r="AH6" s="389" t="s">
         <v>52</v>
       </c>
-      <c r="AI6" s="387" t="s">
+      <c r="AI6" s="389" t="s">
         <v>53</v>
       </c>
-      <c r="AJ6" s="378" t="s">
+      <c r="AJ6" s="380" t="s">
         <v>54</v>
       </c>
-      <c r="AK6" s="378" t="s">
+      <c r="AK6" s="380" t="s">
         <v>55</v>
       </c>
-      <c r="AL6" s="378" t="s">
+      <c r="AL6" s="380" t="s">
         <v>56</v>
       </c>
-      <c r="AM6" s="378" t="s">
+      <c r="AM6" s="380" t="s">
         <v>57</v>
       </c>
-      <c r="AN6" s="381" t="s">
+      <c r="AN6" s="431" t="s">
         <v>58</v>
       </c>
-      <c r="AO6" s="378" t="s">
+      <c r="AO6" s="380" t="s">
         <v>59</v>
       </c>
-      <c r="AP6" s="379"/>
-      <c r="AQ6" s="379"/>
-      <c r="AR6" s="379"/>
-      <c r="AS6" s="379"/>
-      <c r="AT6" s="379"/>
-      <c r="AU6" s="379"/>
-      <c r="AV6" s="379"/>
-      <c r="AW6" s="379"/>
-      <c r="AX6" s="379"/>
-      <c r="AY6" s="342" t="s">
+      <c r="AP6" s="381"/>
+      <c r="AQ6" s="381"/>
+      <c r="AR6" s="381"/>
+      <c r="AS6" s="381"/>
+      <c r="AT6" s="381"/>
+      <c r="AU6" s="381"/>
+      <c r="AV6" s="381"/>
+      <c r="AW6" s="381"/>
+      <c r="AX6" s="381"/>
+      <c r="AY6" s="344" t="s">
         <v>21</v>
       </c>
-      <c r="AZ6" s="384"/>
-      <c r="BA6" s="384"/>
-      <c r="BB6" s="384"/>
-      <c r="BC6" s="384"/>
-      <c r="BD6" s="384"/>
-      <c r="BE6" s="384"/>
-      <c r="BF6" s="384"/>
-      <c r="BG6" s="384"/>
-      <c r="BH6" s="384"/>
-      <c r="BI6" s="384"/>
-      <c r="BJ6" s="385"/>
-      <c r="BK6" s="342" t="s">
+      <c r="AZ6" s="403"/>
+      <c r="BA6" s="403"/>
+      <c r="BB6" s="403"/>
+      <c r="BC6" s="403"/>
+      <c r="BD6" s="403"/>
+      <c r="BE6" s="403"/>
+      <c r="BF6" s="403"/>
+      <c r="BG6" s="403"/>
+      <c r="BH6" s="403"/>
+      <c r="BI6" s="403"/>
+      <c r="BJ6" s="404"/>
+      <c r="BK6" s="344" t="s">
         <v>60</v>
       </c>
-      <c r="BL6" s="384"/>
-      <c r="BM6" s="384"/>
-      <c r="BN6" s="384"/>
-      <c r="BO6" s="384"/>
-      <c r="BP6" s="385"/>
-      <c r="BQ6" s="386" t="s">
+      <c r="BL6" s="403"/>
+      <c r="BM6" s="403"/>
+      <c r="BN6" s="403"/>
+      <c r="BO6" s="403"/>
+      <c r="BP6" s="404"/>
+      <c r="BQ6" s="407" t="s">
         <v>61</v>
       </c>
-      <c r="BR6" s="386" t="s">
+      <c r="BR6" s="407" t="s">
         <v>62</v>
       </c>
-      <c r="BS6" s="386"/>
-      <c r="BT6" s="386"/>
-      <c r="BU6" s="417"/>
-      <c r="BW6" s="398"/>
-      <c r="BX6" s="403"/>
-      <c r="BY6" s="404"/>
-      <c r="BZ6" s="404"/>
-      <c r="CA6" s="405"/>
-      <c r="CB6" s="410"/>
-      <c r="CC6" s="413"/>
-      <c r="CD6" s="413"/>
+      <c r="BS6" s="407"/>
+      <c r="BT6" s="407"/>
+      <c r="BU6" s="408"/>
+      <c r="BW6" s="413"/>
+      <c r="BX6" s="418"/>
+      <c r="BY6" s="419"/>
+      <c r="BZ6" s="419"/>
+      <c r="CA6" s="420"/>
+      <c r="CB6" s="425"/>
+      <c r="CC6" s="401"/>
+      <c r="CD6" s="401"/>
       <c r="CH6" s="112"/>
       <c r="CI6" s="113"/>
     </row>
     <row r="7" spans="1:87" s="111" customFormat="1" ht="12">
-      <c r="A7" s="425"/>
-      <c r="B7" s="428"/>
-      <c r="C7" s="379"/>
-      <c r="D7" s="431"/>
-      <c r="E7" s="431"/>
-      <c r="F7" s="434"/>
-      <c r="G7" s="379"/>
-      <c r="H7" s="388"/>
-      <c r="I7" s="388"/>
-      <c r="J7" s="379"/>
-      <c r="K7" s="391"/>
-      <c r="L7" s="391"/>
-      <c r="M7" s="391"/>
-      <c r="N7" s="391"/>
-      <c r="O7" s="391"/>
-      <c r="P7" s="391"/>
-      <c r="Q7" s="391"/>
-      <c r="R7" s="391"/>
-      <c r="S7" s="391"/>
-      <c r="T7" s="391"/>
-      <c r="U7" s="391"/>
-      <c r="V7" s="395"/>
-      <c r="W7" s="396"/>
-      <c r="X7" s="391"/>
-      <c r="Y7" s="379"/>
-      <c r="Z7" s="379"/>
-      <c r="AA7" s="379"/>
-      <c r="AB7" s="379"/>
-      <c r="AC7" s="388"/>
-      <c r="AD7" s="388"/>
-      <c r="AE7" s="388"/>
-      <c r="AF7" s="388"/>
-      <c r="AG7" s="379"/>
-      <c r="AH7" s="388"/>
-      <c r="AI7" s="388"/>
-      <c r="AJ7" s="379"/>
-      <c r="AK7" s="379"/>
-      <c r="AL7" s="379"/>
-      <c r="AM7" s="379"/>
-      <c r="AN7" s="382"/>
-      <c r="AO7" s="379"/>
-      <c r="AP7" s="379"/>
-      <c r="AQ7" s="379"/>
-      <c r="AR7" s="379"/>
-      <c r="AS7" s="379"/>
-      <c r="AT7" s="379"/>
-      <c r="AU7" s="379"/>
-      <c r="AV7" s="379"/>
-      <c r="AW7" s="379"/>
-      <c r="AX7" s="379"/>
+      <c r="A7" s="375"/>
+      <c r="B7" s="378"/>
+      <c r="C7" s="381"/>
+      <c r="D7" s="384"/>
+      <c r="E7" s="384"/>
+      <c r="F7" s="387"/>
+      <c r="G7" s="381"/>
+      <c r="H7" s="390"/>
+      <c r="I7" s="390"/>
+      <c r="J7" s="381"/>
+      <c r="K7" s="398"/>
+      <c r="L7" s="398"/>
+      <c r="M7" s="398"/>
+      <c r="N7" s="398"/>
+      <c r="O7" s="398"/>
+      <c r="P7" s="398"/>
+      <c r="Q7" s="398"/>
+      <c r="R7" s="398"/>
+      <c r="S7" s="398"/>
+      <c r="T7" s="398"/>
+      <c r="U7" s="398"/>
+      <c r="V7" s="429"/>
+      <c r="W7" s="430"/>
+      <c r="X7" s="398"/>
+      <c r="Y7" s="381"/>
+      <c r="Z7" s="381"/>
+      <c r="AA7" s="381"/>
+      <c r="AB7" s="381"/>
+      <c r="AC7" s="390"/>
+      <c r="AD7" s="390"/>
+      <c r="AE7" s="390"/>
+      <c r="AF7" s="390"/>
+      <c r="AG7" s="381"/>
+      <c r="AH7" s="390"/>
+      <c r="AI7" s="390"/>
+      <c r="AJ7" s="381"/>
+      <c r="AK7" s="381"/>
+      <c r="AL7" s="381"/>
+      <c r="AM7" s="381"/>
+      <c r="AN7" s="432"/>
+      <c r="AO7" s="381"/>
+      <c r="AP7" s="381"/>
+      <c r="AQ7" s="381"/>
+      <c r="AR7" s="381"/>
+      <c r="AS7" s="381"/>
+      <c r="AT7" s="381"/>
+      <c r="AU7" s="381"/>
+      <c r="AV7" s="381"/>
+      <c r="AW7" s="381"/>
+      <c r="AX7" s="381"/>
       <c r="AY7" s="88" t="s">
         <v>63</v>
       </c>
@@ -18711,122 +18712,122 @@
       <c r="BA7" s="88" t="s">
         <v>65</v>
       </c>
-      <c r="BB7" s="354" t="s">
+      <c r="BB7" s="338" t="s">
         <v>66</v>
       </c>
-      <c r="BC7" s="374" t="s">
+      <c r="BC7" s="410" t="s">
         <v>67</v>
       </c>
-      <c r="BD7" s="374" t="s">
+      <c r="BD7" s="410" t="s">
         <v>68</v>
       </c>
-      <c r="BE7" s="374" t="s">
+      <c r="BE7" s="410" t="s">
         <v>121</v>
       </c>
-      <c r="BF7" s="374" t="s">
+      <c r="BF7" s="410" t="s">
         <v>70</v>
       </c>
-      <c r="BG7" s="374" t="s">
+      <c r="BG7" s="410" t="s">
         <v>71</v>
       </c>
-      <c r="BH7" s="374" t="s">
+      <c r="BH7" s="410" t="s">
         <v>72</v>
       </c>
-      <c r="BI7" s="374" t="s">
+      <c r="BI7" s="410" t="s">
         <v>75</v>
       </c>
-      <c r="BJ7" s="376" t="s">
+      <c r="BJ7" s="434" t="s">
         <v>76</v>
       </c>
-      <c r="BK7" s="374" t="s">
+      <c r="BK7" s="410" t="s">
         <v>77</v>
       </c>
-      <c r="BL7" s="354" t="s">
+      <c r="BL7" s="338" t="s">
         <v>78</v>
       </c>
-      <c r="BM7" s="374" t="s">
+      <c r="BM7" s="410" t="s">
         <v>79</v>
       </c>
-      <c r="BN7" s="354" t="s">
+      <c r="BN7" s="338" t="s">
         <v>80</v>
       </c>
-      <c r="BO7" s="354" t="s">
+      <c r="BO7" s="338" t="s">
         <v>122</v>
       </c>
-      <c r="BP7" s="354" t="s">
+      <c r="BP7" s="338" t="s">
         <v>81</v>
       </c>
-      <c r="BQ7" s="386"/>
-      <c r="BR7" s="386"/>
-      <c r="BS7" s="386"/>
-      <c r="BT7" s="386"/>
-      <c r="BU7" s="417"/>
-      <c r="BW7" s="398"/>
-      <c r="BX7" s="406"/>
-      <c r="BY7" s="407"/>
-      <c r="BZ7" s="407"/>
-      <c r="CA7" s="408"/>
-      <c r="CB7" s="410"/>
-      <c r="CC7" s="413"/>
-      <c r="CD7" s="413"/>
+      <c r="BQ7" s="407"/>
+      <c r="BR7" s="407"/>
+      <c r="BS7" s="407"/>
+      <c r="BT7" s="407"/>
+      <c r="BU7" s="408"/>
+      <c r="BW7" s="413"/>
+      <c r="BX7" s="421"/>
+      <c r="BY7" s="422"/>
+      <c r="BZ7" s="422"/>
+      <c r="CA7" s="423"/>
+      <c r="CB7" s="425"/>
+      <c r="CC7" s="401"/>
+      <c r="CD7" s="401"/>
       <c r="CH7" s="112"/>
       <c r="CI7" s="113"/>
     </row>
     <row r="8" spans="1:87" s="111" customFormat="1" ht="24">
-      <c r="A8" s="426"/>
-      <c r="B8" s="429"/>
-      <c r="C8" s="380"/>
-      <c r="D8" s="432"/>
-      <c r="E8" s="432"/>
-      <c r="F8" s="435"/>
-      <c r="G8" s="380"/>
-      <c r="H8" s="389"/>
-      <c r="I8" s="389"/>
-      <c r="J8" s="380"/>
-      <c r="K8" s="392"/>
-      <c r="L8" s="392"/>
-      <c r="M8" s="392"/>
-      <c r="N8" s="392"/>
-      <c r="O8" s="392"/>
-      <c r="P8" s="392"/>
-      <c r="Q8" s="392"/>
-      <c r="R8" s="392"/>
-      <c r="S8" s="392"/>
-      <c r="T8" s="392"/>
-      <c r="U8" s="392"/>
+      <c r="A8" s="376"/>
+      <c r="B8" s="379"/>
+      <c r="C8" s="382"/>
+      <c r="D8" s="385"/>
+      <c r="E8" s="385"/>
+      <c r="F8" s="388"/>
+      <c r="G8" s="382"/>
+      <c r="H8" s="391"/>
+      <c r="I8" s="391"/>
+      <c r="J8" s="382"/>
+      <c r="K8" s="399"/>
+      <c r="L8" s="399"/>
+      <c r="M8" s="399"/>
+      <c r="N8" s="399"/>
+      <c r="O8" s="399"/>
+      <c r="P8" s="399"/>
+      <c r="Q8" s="399"/>
+      <c r="R8" s="399"/>
+      <c r="S8" s="399"/>
+      <c r="T8" s="399"/>
+      <c r="U8" s="399"/>
       <c r="V8" s="115" t="s">
         <v>82</v>
       </c>
       <c r="W8" s="115" t="s">
         <v>83</v>
       </c>
-      <c r="X8" s="392"/>
-      <c r="Y8" s="380"/>
-      <c r="Z8" s="380"/>
-      <c r="AA8" s="380"/>
-      <c r="AB8" s="380"/>
-      <c r="AC8" s="389"/>
-      <c r="AD8" s="389"/>
-      <c r="AE8" s="389"/>
-      <c r="AF8" s="389"/>
-      <c r="AG8" s="380"/>
-      <c r="AH8" s="389"/>
-      <c r="AI8" s="389"/>
-      <c r="AJ8" s="380"/>
-      <c r="AK8" s="380"/>
-      <c r="AL8" s="380"/>
-      <c r="AM8" s="380"/>
-      <c r="AN8" s="383"/>
-      <c r="AO8" s="380"/>
-      <c r="AP8" s="380"/>
-      <c r="AQ8" s="380"/>
-      <c r="AR8" s="380"/>
-      <c r="AS8" s="380"/>
-      <c r="AT8" s="380"/>
-      <c r="AU8" s="380"/>
-      <c r="AV8" s="380"/>
-      <c r="AW8" s="380"/>
-      <c r="AX8" s="380"/>
+      <c r="X8" s="399"/>
+      <c r="Y8" s="382"/>
+      <c r="Z8" s="382"/>
+      <c r="AA8" s="382"/>
+      <c r="AB8" s="382"/>
+      <c r="AC8" s="391"/>
+      <c r="AD8" s="391"/>
+      <c r="AE8" s="391"/>
+      <c r="AF8" s="391"/>
+      <c r="AG8" s="382"/>
+      <c r="AH8" s="391"/>
+      <c r="AI8" s="391"/>
+      <c r="AJ8" s="382"/>
+      <c r="AK8" s="382"/>
+      <c r="AL8" s="382"/>
+      <c r="AM8" s="382"/>
+      <c r="AN8" s="433"/>
+      <c r="AO8" s="382"/>
+      <c r="AP8" s="382"/>
+      <c r="AQ8" s="382"/>
+      <c r="AR8" s="382"/>
+      <c r="AS8" s="382"/>
+      <c r="AT8" s="382"/>
+      <c r="AU8" s="382"/>
+      <c r="AV8" s="382"/>
+      <c r="AW8" s="382"/>
+      <c r="AX8" s="382"/>
       <c r="AY8" s="89" t="s">
         <v>84</v>
       </c>
@@ -18836,27 +18837,27 @@
       <c r="BA8" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="BB8" s="355"/>
-      <c r="BC8" s="375"/>
-      <c r="BD8" s="375"/>
-      <c r="BE8" s="375"/>
-      <c r="BF8" s="375"/>
-      <c r="BG8" s="375"/>
-      <c r="BH8" s="375"/>
-      <c r="BI8" s="375"/>
-      <c r="BJ8" s="377"/>
-      <c r="BK8" s="375"/>
-      <c r="BL8" s="355"/>
-      <c r="BM8" s="375"/>
-      <c r="BN8" s="355"/>
-      <c r="BO8" s="355"/>
-      <c r="BP8" s="355"/>
-      <c r="BQ8" s="355"/>
-      <c r="BR8" s="355"/>
-      <c r="BS8" s="355"/>
-      <c r="BT8" s="355"/>
-      <c r="BU8" s="418"/>
-      <c r="BW8" s="399"/>
+      <c r="BB8" s="340"/>
+      <c r="BC8" s="411"/>
+      <c r="BD8" s="411"/>
+      <c r="BE8" s="411"/>
+      <c r="BF8" s="411"/>
+      <c r="BG8" s="411"/>
+      <c r="BH8" s="411"/>
+      <c r="BI8" s="411"/>
+      <c r="BJ8" s="435"/>
+      <c r="BK8" s="411"/>
+      <c r="BL8" s="340"/>
+      <c r="BM8" s="411"/>
+      <c r="BN8" s="340"/>
+      <c r="BO8" s="340"/>
+      <c r="BP8" s="340"/>
+      <c r="BQ8" s="340"/>
+      <c r="BR8" s="340"/>
+      <c r="BS8" s="340"/>
+      <c r="BT8" s="340"/>
+      <c r="BU8" s="409"/>
+      <c r="BW8" s="414"/>
       <c r="BX8" s="61" t="s">
         <v>87</v>
       </c>
@@ -18869,9 +18870,9 @@
       <c r="CA8" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="CB8" s="411"/>
-      <c r="CC8" s="414"/>
-      <c r="CD8" s="414"/>
+      <c r="CB8" s="426"/>
+      <c r="CC8" s="402"/>
+      <c r="CD8" s="402"/>
       <c r="CF8" s="116"/>
       <c r="CH8" s="112"/>
       <c r="CI8" s="113"/>
@@ -21303,6 +21304,72 @@
     </row>
   </sheetData>
   <mergeCells count="82">
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="BQ6:BQ8"/>
+    <mergeCell ref="BB7:BB8"/>
+    <mergeCell ref="BC7:BC8"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="AY6:BJ6"/>
+    <mergeCell ref="BK6:BP6"/>
+    <mergeCell ref="BO7:BO8"/>
+    <mergeCell ref="BP7:BP8"/>
+    <mergeCell ref="BI7:BI8"/>
+    <mergeCell ref="BJ7:BJ8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="BX5:CA7"/>
+    <mergeCell ref="CB5:CB8"/>
+    <mergeCell ref="CC5:CC8"/>
+    <mergeCell ref="AR5:AR8"/>
+    <mergeCell ref="AS5:AS8"/>
+    <mergeCell ref="AT5:AT8"/>
+    <mergeCell ref="AU5:AU8"/>
+    <mergeCell ref="AV5:AV8"/>
+    <mergeCell ref="AW5:AW8"/>
+    <mergeCell ref="BK7:BK8"/>
+    <mergeCell ref="BL7:BL8"/>
+    <mergeCell ref="BM7:BM8"/>
+    <mergeCell ref="BN7:BN8"/>
+    <mergeCell ref="BF7:BF8"/>
+    <mergeCell ref="BG7:BG8"/>
+    <mergeCell ref="BH7:BH8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="BW5:BW8"/>
+    <mergeCell ref="AQ5:AQ8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="CD5:CD8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="AY5:BP5"/>
+    <mergeCell ref="BQ5:BR5"/>
+    <mergeCell ref="BS5:BS8"/>
+    <mergeCell ref="BT5:BT8"/>
+    <mergeCell ref="BU5:BU8"/>
+    <mergeCell ref="BR6:BR8"/>
     <mergeCell ref="A3:BU3"/>
     <mergeCell ref="BW3:CB4"/>
     <mergeCell ref="A5:A8"/>
@@ -21319,72 +21386,6 @@
     <mergeCell ref="Y5:AO5"/>
     <mergeCell ref="AP5:AP8"/>
     <mergeCell ref="P6:P8"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="CD5:CD8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="AY5:BP5"/>
-    <mergeCell ref="BQ5:BR5"/>
-    <mergeCell ref="BS5:BS8"/>
-    <mergeCell ref="BT5:BT8"/>
-    <mergeCell ref="BU5:BU8"/>
-    <mergeCell ref="BR6:BR8"/>
-    <mergeCell ref="BF7:BF8"/>
-    <mergeCell ref="BG7:BG8"/>
-    <mergeCell ref="BH7:BH8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="BW5:BW8"/>
-    <mergeCell ref="BX5:CA7"/>
-    <mergeCell ref="CB5:CB8"/>
-    <mergeCell ref="CC5:CC8"/>
-    <mergeCell ref="AR5:AR8"/>
-    <mergeCell ref="AS5:AS8"/>
-    <mergeCell ref="AT5:AT8"/>
-    <mergeCell ref="AU5:AU8"/>
-    <mergeCell ref="AV5:AV8"/>
-    <mergeCell ref="AW5:AW8"/>
-    <mergeCell ref="AQ5:AQ8"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="BQ6:BQ8"/>
-    <mergeCell ref="BB7:BB8"/>
-    <mergeCell ref="BC7:BC8"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="AY6:BJ6"/>
-    <mergeCell ref="BK6:BP6"/>
-    <mergeCell ref="BO7:BO8"/>
-    <mergeCell ref="BP7:BP8"/>
-    <mergeCell ref="BI7:BI8"/>
-    <mergeCell ref="BJ7:BJ8"/>
-    <mergeCell ref="BK7:BK8"/>
-    <mergeCell ref="BL7:BL8"/>
-    <mergeCell ref="BM7:BM8"/>
-    <mergeCell ref="BN7:BN8"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B4 B12:B16 B20 B9:BU9">
     <cfRule type="duplicateValues" dxfId="9" priority="9"/>
@@ -21393,17 +21394,17 @@
     <cfRule type="duplicateValues" dxfId="8" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:B8">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
     <cfRule type="duplicateValues" dxfId="6" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:B16 B1:B4 B20 B9:BU9">
     <cfRule type="duplicateValues" dxfId="4" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
     <cfRule type="duplicateValues" dxfId="2" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="BJ10">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
